--- a/data/leagues/Brown Munde 2026.xlsx
+++ b/data/leagues/Brown Munde 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="96">
   <si>
     <t>Still Rollin'</t>
   </si>
@@ -55,10 +55,13 @@
     <t>BurgerBoyz</t>
   </si>
   <si>
-    <t>1-0-0</t>
-  </si>
-  <si>
-    <t>0-1-0</t>
+    <t>1-1-0</t>
+  </si>
+  <si>
+    <t>2-0-0</t>
+  </si>
+  <si>
+    <t>0-2-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -118,6 +121,9 @@
     <t>Week_2</t>
   </si>
   <si>
+    <t>Week_3</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -148,21 +154,21 @@
     <t>suraj bhalani</t>
   </si>
   <si>
+    <t>Krishna Padodara</t>
+  </si>
+  <si>
+    <t>KASHYAP AShok</t>
+  </si>
+  <si>
+    <t>Pawan Bhambhwani</t>
+  </si>
+  <si>
+    <t>Prahlad Singh</t>
+  </si>
+  <si>
     <t>Kiran MADUGULA</t>
   </si>
   <si>
-    <t>Pawan Bhambhwani</t>
-  </si>
-  <si>
-    <t>KASHYAP AShok</t>
-  </si>
-  <si>
-    <t>Prahlad Singh</t>
-  </si>
-  <si>
-    <t>Krishna Padodara</t>
-  </si>
-  <si>
     <t>Harshit Aggarwal</t>
   </si>
   <si>
@@ -193,63 +199,63 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>1-0</t>
-  </si>
-  <si>
-    <t>0-1</t>
-  </si>
-  <si>
-    <t>11.8-2.1-0.1</t>
-  </si>
-  <si>
-    <t>12.9-1.1</t>
-  </si>
-  <si>
-    <t>10.7-3.2-0.1</t>
-  </si>
-  <si>
-    <t>7.2-6.7-0.1</t>
-  </si>
-  <si>
-    <t>6.8-7.1-0.1</t>
-  </si>
-  <si>
-    <t>6.0-7.9-0.1</t>
-  </si>
-  <si>
-    <t>5.3-8.6-0.1</t>
-  </si>
-  <si>
-    <t>3.7-10.2-0.1</t>
-  </si>
-  <si>
-    <t>1.4-12.6-0.1</t>
-  </si>
-  <si>
-    <t>12-2</t>
-  </si>
-  <si>
-    <t>13-1</t>
-  </si>
-  <si>
-    <t>11-3</t>
+    <t>1-1</t>
+  </si>
+  <si>
+    <t>2-0</t>
+  </si>
+  <si>
+    <t>0-2</t>
+  </si>
+  <si>
+    <t>9.3-4.6-0.1</t>
+  </si>
+  <si>
+    <t>8.5-5.4-0.1</t>
+  </si>
+  <si>
+    <t>8.2-5.8-0.1</t>
+  </si>
+  <si>
+    <t>7.7-6.2-0.1</t>
+  </si>
+  <si>
+    <t>7.9-6.1-0.1</t>
+  </si>
+  <si>
+    <t>6.7-7.2-0.1</t>
+  </si>
+  <si>
+    <t>6.5-7.4-0.1</t>
+  </si>
+  <si>
+    <t>5.5-8.4-0.1</t>
+  </si>
+  <si>
+    <t>5.6-8.4-0.1</t>
+  </si>
+  <si>
+    <t>3.8-10.1-0.1</t>
+  </si>
+  <si>
+    <t>9-5</t>
+  </si>
+  <si>
+    <t>8-6</t>
   </si>
   <si>
     <t>7-7</t>
   </si>
   <si>
+    <t>5-9</t>
+  </si>
+  <si>
     <t>6-8</t>
   </si>
   <si>
-    <t>5-9</t>
-  </si>
-  <si>
     <t>4-10</t>
   </si>
   <si>
-    <t>1-13</t>
-  </si>
-  <si>
     <t>Owners</t>
   </si>
   <si>
@@ -259,7 +265,31 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>↑2</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>↑1</t>
+  </si>
+  <si>
+    <t>↓3</t>
+  </si>
+  <si>
+    <t>↑3</t>
+  </si>
+  <si>
+    <t>↓1</t>
+  </si>
+  <si>
+    <t>↓2</t>
+  </si>
+  <si>
     <t>Week 1</t>
+  </si>
+  <si>
+    <t>Week 2</t>
   </si>
   <si>
     <t>Week</t>
@@ -681,13 +711,13 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
         <v>10</v>
@@ -699,10 +729,10 @@
         <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K2" t="s">
         <v>10</v>
@@ -713,34 +743,34 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
       <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3" t="s">
         <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" t="s">
-        <v>11</v>
-      </c>
-      <c r="K3" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -751,13 +781,13 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
         <v>10</v>
@@ -786,31 +816,31 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
         <v>11</v>
       </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>11</v>
       </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" t="s">
-        <v>10</v>
-      </c>
       <c r="H5" t="s">
         <v>10</v>
       </c>
       <c r="I5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" t="s">
         <v>11</v>
-      </c>
-      <c r="J5" t="s">
-        <v>11</v>
-      </c>
-      <c r="K5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -818,34 +848,34 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K6" t="s">
         <v>11</v>
-      </c>
-      <c r="C6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I6" t="s">
-        <v>11</v>
-      </c>
-      <c r="J6" t="s">
-        <v>11</v>
-      </c>
-      <c r="K6" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -853,34 +883,34 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -891,31 +921,31 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
       </c>
       <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J8" t="s">
+        <v>10</v>
+      </c>
+      <c r="K8" t="s">
         <v>11</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" t="s">
-        <v>10</v>
-      </c>
-      <c r="I8" t="s">
-        <v>10</v>
-      </c>
-      <c r="J8" t="s">
-        <v>10</v>
-      </c>
-      <c r="K8" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -923,34 +953,34 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" t="s">
+        <v>10</v>
+      </c>
+      <c r="J9" t="s">
+        <v>10</v>
+      </c>
+      <c r="K9" t="s">
         <v>11</v>
-      </c>
-      <c r="C9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" t="s">
-        <v>11</v>
-      </c>
-      <c r="K9" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -961,19 +991,19 @@
         <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
         <v>10</v>
       </c>
       <c r="G10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H10" t="s">
         <v>10</v>
@@ -985,7 +1015,7 @@
         <v>10</v>
       </c>
       <c r="K10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -993,34 +1023,34 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" t="s">
         <v>11</v>
       </c>
-      <c r="D11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="H11" t="s">
         <v>11</v>
       </c>
-      <c r="F11" t="s">
+      <c r="I11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11" t="s">
+        <v>10</v>
+      </c>
+      <c r="K11" t="s">
         <v>11</v>
-      </c>
-      <c r="G11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" t="s">
-        <v>10</v>
-      </c>
-      <c r="I11" t="s">
-        <v>11</v>
-      </c>
-      <c r="J11" t="s">
-        <v>11</v>
-      </c>
-      <c r="K11" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1030,30 +1060,108 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:H1"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:8">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2">
+        <v>10</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>9</v>
+      </c>
+      <c r="H2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3">
+        <v>-7</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>8</v>
+      </c>
+      <c r="H3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>-4</v>
+      </c>
+      <c r="F4">
+        <v>-2</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1068,13 +1176,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1082,13 +1190,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C2">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1096,13 +1204,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1113,10 +1221,10 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1124,10 +1232,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
@@ -1138,13 +1246,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1152,13 +1260,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1169,7 +1277,7 @@
         <v>6</v>
       </c>
       <c r="C8">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -1180,10 +1288,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -1194,10 +1302,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C10">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
@@ -1211,10 +1319,10 @@
         <v>9</v>
       </c>
       <c r="C11">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1229,16 +1337,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1246,16 +1354,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1263,13 +1371,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="D3">
-        <v>-0.09999999999999998</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -1280,13 +1388,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="D4">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -1297,13 +1405,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="D5">
-        <v>-0.4</v>
+        <v>0.2</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -1314,16 +1422,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="D6">
-        <v>0.6</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1331,13 +1439,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="D7">
-        <v>-0.5</v>
+        <v>-0.09999999999999998</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -1348,16 +1456,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="D8">
-        <v>0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1365,16 +1473,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="D9">
-        <v>0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1382,16 +1490,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C10">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="D10">
-        <v>0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1399,16 +1507,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1423,420 +1531,420 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="C2">
-        <v>57.1</v>
+        <v>22.2</v>
       </c>
       <c r="D2">
-        <v>22.7</v>
+        <v>13.4</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>7.9</v>
       </c>
       <c r="F2">
+        <v>6.2</v>
+      </c>
+      <c r="G2">
+        <v>3.3</v>
+      </c>
+      <c r="H2">
+        <v>1.9</v>
+      </c>
+      <c r="I2">
+        <v>0.9</v>
+      </c>
+      <c r="J2">
         <v>0.1</v>
       </c>
-      <c r="G2">
+      <c r="K2">
         <v>0.1</v>
       </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
       <c r="L2">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3">
-        <v>75.8</v>
+        <v>15.7</v>
       </c>
       <c r="C3">
-        <v>20.1</v>
+        <v>19.5</v>
       </c>
       <c r="D3">
-        <v>4.1</v>
+        <v>18.9</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L3">
-        <v>100</v>
+        <v>87.40000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>15.3</v>
       </c>
       <c r="C4">
-        <v>22.1</v>
+        <v>19.4</v>
       </c>
       <c r="D4">
-        <v>66.3</v>
+        <v>17.2</v>
       </c>
       <c r="E4">
-        <v>4.9</v>
+        <v>13.6</v>
       </c>
       <c r="F4">
-        <v>1.3</v>
+        <v>12.3</v>
       </c>
       <c r="G4">
-        <v>0.3</v>
+        <v>8.6</v>
       </c>
       <c r="H4">
-        <v>0.1</v>
+        <v>6.4</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L4">
-        <v>99.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B5">
-        <v>0.2</v>
+        <v>6.4</v>
       </c>
       <c r="C5">
-        <v>0.5</v>
+        <v>11.5</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>16.1</v>
       </c>
       <c r="E5">
-        <v>35.9</v>
+        <v>20.2</v>
       </c>
       <c r="F5">
-        <v>33.5</v>
+        <v>17.2</v>
       </c>
       <c r="G5">
-        <v>15.5</v>
+        <v>12.6</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="I5">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="J5">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L5">
-        <v>88.59999999999999</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>12.8</v>
       </c>
       <c r="C6">
-        <v>0.1</v>
+        <v>15.5</v>
       </c>
       <c r="D6">
-        <v>2.8</v>
+        <v>15.4</v>
       </c>
       <c r="E6">
-        <v>37.3</v>
+        <v>16.1</v>
       </c>
       <c r="F6">
-        <v>27.6</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>18.4</v>
+        <v>10.6</v>
       </c>
       <c r="H6">
         <v>8</v>
       </c>
       <c r="I6">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L6">
-        <v>86.2</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="D7">
-        <v>0.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E7">
-        <v>13.4</v>
+        <v>9.1</v>
       </c>
       <c r="F7">
-        <v>20</v>
+        <v>14.3</v>
       </c>
       <c r="G7">
-        <v>28.2</v>
+        <v>14.8</v>
       </c>
       <c r="H7">
-        <v>21.2</v>
+        <v>15.3</v>
       </c>
       <c r="I7">
-        <v>11.4</v>
+        <v>13.9</v>
       </c>
       <c r="J7">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="K7">
-        <v>0.1</v>
+        <v>5.3</v>
       </c>
       <c r="L7">
-        <v>62.4</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="C8">
-        <v>0.1</v>
+        <v>3.8</v>
       </c>
       <c r="D8">
-        <v>0.2</v>
+        <v>5.1</v>
       </c>
       <c r="E8">
-        <v>6.2</v>
+        <v>10.6</v>
       </c>
       <c r="F8">
-        <v>13.4</v>
+        <v>14.2</v>
       </c>
       <c r="G8">
-        <v>24.5</v>
+        <v>16.5</v>
       </c>
       <c r="H8">
-        <v>31.7</v>
+        <v>18.2</v>
       </c>
       <c r="I8">
-        <v>16.7</v>
+        <v>14.1</v>
       </c>
       <c r="J8">
-        <v>5.9</v>
+        <v>9.6</v>
       </c>
       <c r="K8">
-        <v>1.3</v>
+        <v>6.4</v>
       </c>
       <c r="L8">
-        <v>44.4</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="D9">
-        <v>0.1</v>
+        <v>2.6</v>
       </c>
       <c r="E9">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="F9">
-        <v>2.6</v>
+        <v>6</v>
       </c>
       <c r="G9">
-        <v>6.9</v>
+        <v>13.2</v>
       </c>
       <c r="H9">
-        <v>13.8</v>
+        <v>14.5</v>
       </c>
       <c r="I9">
-        <v>31.5</v>
+        <v>19.1</v>
       </c>
       <c r="J9">
-        <v>39.3</v>
+        <v>22.3</v>
       </c>
       <c r="K9">
-        <v>4.9</v>
+        <v>17</v>
       </c>
       <c r="L9">
-        <v>10.5</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="E10">
-        <v>0.4</v>
+        <v>5.1</v>
       </c>
       <c r="F10">
-        <v>1.5</v>
+        <v>6.6</v>
       </c>
       <c r="G10">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="H10">
-        <v>16.3</v>
+        <v>14.1</v>
       </c>
       <c r="I10">
-        <v>30.7</v>
+        <v>20.5</v>
       </c>
       <c r="J10">
-        <v>36.6</v>
+        <v>24.9</v>
       </c>
       <c r="K10">
-        <v>8.5</v>
+        <v>16.1</v>
       </c>
       <c r="L10">
-        <v>7.9</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="G11">
-        <v>0.1</v>
+        <v>2.1</v>
       </c>
       <c r="H11">
-        <v>0.5</v>
+        <v>6</v>
       </c>
       <c r="I11">
-        <v>2.7</v>
+        <v>12.1</v>
       </c>
       <c r="J11">
-        <v>11.5</v>
+        <v>24.8</v>
       </c>
       <c r="K11">
-        <v>85.2</v>
+        <v>53</v>
       </c>
       <c r="L11">
-        <v>0.1</v>
+        <v>4.1</v>
       </c>
     </row>
   </sheetData>
@@ -1846,125 +1954,158 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>31</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2">
         <v>100</v>
       </c>
       <c r="C2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>96.89999999999999</v>
+      </c>
+      <c r="D2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3">
-        <v>100</v>
+        <v>71.89999999999999</v>
       </c>
       <c r="C3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>91.7</v>
+      </c>
+      <c r="D3">
+        <v>88.40000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B4">
         <v>100</v>
       </c>
       <c r="C4">
-        <v>99.90000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>89.60000000000001</v>
+      </c>
+      <c r="D4">
+        <v>85.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B5">
-        <v>90.2</v>
+        <v>36.2</v>
       </c>
       <c r="C5">
-        <v>89.2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="D5">
+        <v>83.09999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B6">
-        <v>82.89999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="C6">
-        <v>88.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="D6">
+        <v>81.89999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B7">
-        <v>70.7</v>
+        <v>100</v>
       </c>
       <c r="C7">
-        <v>60.2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>47.2</v>
+      </c>
+      <c r="D7">
+        <v>56.89999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B8">
-        <v>36.5</v>
+        <v>8</v>
       </c>
       <c r="C8">
-        <v>43.4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>46</v>
+      </c>
+      <c r="D8">
+        <v>50.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9">
+        <v>0.1</v>
+      </c>
+      <c r="C9">
+        <v>27.8</v>
+      </c>
+      <c r="D9">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="C10">
+        <v>21.7</v>
+      </c>
+      <c r="D10">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B9">
-        <v>12</v>
-      </c>
-      <c r="C9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10">
-        <v>7.5</v>
-      </c>
-      <c r="C10">
-        <v>8.699999999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="B11">
-        <v>0.2</v>
+        <v>8.799999999999999</v>
       </c>
       <c r="C11">
-        <v>0.1</v>
+        <v>2.1</v>
+      </c>
+      <c r="D11">
+        <v>4.5</v>
       </c>
     </row>
   </sheetData>
@@ -1979,28 +2120,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2011,25 +2152,25 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D2">
-        <v>104.36</v>
+        <v>121.69</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>120.5</v>
+        <v>117.7</v>
       </c>
       <c r="G2">
-        <v>0.462</v>
+        <v>0.417</v>
       </c>
       <c r="H2">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="I2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2040,25 +2181,25 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D3">
-        <v>92.56</v>
+        <v>99.31999999999999</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>122.32</v>
+        <v>119.67</v>
       </c>
       <c r="G3">
-        <v>0.615</v>
+        <v>0.583</v>
       </c>
       <c r="H3">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2069,25 +2210,25 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D4">
-        <v>60.92</v>
+        <v>94.45</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>123.1</v>
+        <v>118.25</v>
       </c>
       <c r="G4">
-        <v>0.538</v>
+        <v>0.5</v>
       </c>
       <c r="H4">
         <v>0.8</v>
       </c>
       <c r="I4">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2095,28 +2236,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D5">
-        <v>89.95999999999999</v>
+        <v>130.84</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>121.04</v>
+        <v>113.95</v>
       </c>
       <c r="G5">
-        <v>0.538</v>
+        <v>0.5</v>
       </c>
       <c r="H5">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="I5">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2124,28 +2265,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D6">
-        <v>144.1</v>
+        <v>128.91</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6">
-        <v>109.53</v>
+        <v>115.73</v>
       </c>
       <c r="G6">
-        <v>0.385</v>
+        <v>0.5</v>
       </c>
       <c r="H6">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2153,28 +2294,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D7">
-        <v>104.14</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>117.84</v>
+        <v>114.44</v>
       </c>
       <c r="G7">
-        <v>0.538</v>
+        <v>0.5</v>
       </c>
       <c r="H7">
         <v>-0.2</v>
       </c>
       <c r="I7">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2185,25 +2326,25 @@
         <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D8">
-        <v>115.26</v>
+        <v>100.77</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
       <c r="F8">
-        <v>119.14</v>
+        <v>116.96</v>
       </c>
       <c r="G8">
-        <v>0.538</v>
+        <v>0.458</v>
       </c>
       <c r="H8">
         <v>-0.3</v>
       </c>
       <c r="I8">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2211,28 +2352,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D9">
-        <v>157.22</v>
+        <v>110.4</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9">
-        <v>107.43</v>
+        <v>117.41</v>
       </c>
       <c r="G9">
-        <v>0.385</v>
+        <v>0.5</v>
       </c>
       <c r="H9">
-        <v>-0.6</v>
+        <v>-0.4</v>
       </c>
       <c r="I9">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2243,25 +2384,25 @@
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D10">
-        <v>121.9</v>
+        <v>121.93</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F10">
-        <v>118.62</v>
+        <v>117.06</v>
       </c>
       <c r="G10">
-        <v>0.615</v>
+        <v>0.542</v>
       </c>
       <c r="H10">
         <v>-0.8</v>
       </c>
       <c r="I10">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2272,25 +2413,25 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D11">
-        <v>175.36</v>
+        <v>147.78</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11">
-        <v>106.26</v>
+        <v>113.94</v>
       </c>
       <c r="G11">
-        <v>0.385</v>
+        <v>0.5</v>
       </c>
       <c r="H11">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="I11">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2305,321 +2446,321 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D2">
-        <v>157.22</v>
+        <v>147.78</v>
       </c>
       <c r="E2">
-        <v>157.22</v>
+        <v>295.56</v>
       </c>
       <c r="F2">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>175.36</v>
+        <v>121.69</v>
       </c>
       <c r="E3">
-        <v>175.36</v>
+        <v>243.38</v>
       </c>
       <c r="F3">
-        <v>100</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D4">
-        <v>144.1</v>
+        <v>130.84</v>
       </c>
       <c r="E4">
-        <v>144.1</v>
+        <v>261.68</v>
       </c>
       <c r="F4">
-        <v>99.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D5">
-        <v>115.26</v>
+        <v>121.93</v>
       </c>
       <c r="E5">
-        <v>115.26</v>
+        <v>243.86</v>
       </c>
       <c r="F5">
-        <v>88.59999999999999</v>
+        <v>84</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="H5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D6">
-        <v>121.9</v>
+        <v>128.91</v>
       </c>
       <c r="E6">
-        <v>121.9</v>
+        <v>257.82</v>
       </c>
       <c r="F6">
-        <v>86.2</v>
+        <v>82.39999999999999</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="H6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
-        <v>104.36</v>
+        <v>109</v>
       </c>
       <c r="E7">
-        <v>104.36</v>
+        <v>218</v>
       </c>
       <c r="F7">
-        <v>62.4</v>
+        <v>55.50000000000001</v>
       </c>
       <c r="G7">
-        <v>0.1</v>
+        <v>5.3</v>
       </c>
       <c r="H7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D8">
-        <v>104.14</v>
+        <v>110.4</v>
       </c>
       <c r="E8">
-        <v>104.14</v>
+        <v>220.8</v>
       </c>
       <c r="F8">
-        <v>44.4</v>
+        <v>51.7</v>
       </c>
       <c r="G8">
-        <v>1.3</v>
+        <v>6.4</v>
       </c>
       <c r="H8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D9">
-        <v>92.56</v>
+        <v>100.77</v>
       </c>
       <c r="E9">
-        <v>92.56</v>
+        <v>201.54</v>
       </c>
       <c r="F9">
-        <v>10.5</v>
+        <v>27.1</v>
       </c>
       <c r="G9">
-        <v>4.9</v>
+        <v>17</v>
       </c>
       <c r="H9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D10">
-        <v>89.95999999999999</v>
+        <v>94.45</v>
       </c>
       <c r="E10">
-        <v>89.95999999999999</v>
+        <v>188.9</v>
       </c>
       <c r="F10">
-        <v>7.9</v>
+        <v>24.4</v>
       </c>
       <c r="G10">
-        <v>8.5</v>
+        <v>16.1</v>
       </c>
       <c r="H10" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>60.92</v>
+        <v>99.31999999999999</v>
       </c>
       <c r="E11">
-        <v>60.92</v>
+        <v>198.64</v>
       </c>
       <c r="F11">
-        <v>0.1</v>
+        <v>4.100000000000001</v>
       </c>
       <c r="G11">
-        <v>85.2</v>
+        <v>53</v>
       </c>
       <c r="H11" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2634,19 +2775,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2657,16 +2798,16 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="F2">
-        <v>0</v>
+      <c r="F2" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2677,16 +2818,16 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D3">
         <v>6</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2694,19 +2835,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
-      <c r="F4">
-        <v>0</v>
+      <c r="F4" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2714,7 +2855,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
         <v>43</v>
@@ -2723,10 +2864,10 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2734,19 +2875,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
-      <c r="F6">
-        <v>0</v>
+      <c r="F6" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2754,10 +2895,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7">
         <v>-1</v>
@@ -2765,8 +2906,8 @@
       <c r="E7" t="s">
         <v>10</v>
       </c>
-      <c r="F7">
-        <v>0</v>
+      <c r="F7" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2774,19 +2915,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D8">
         <v>-2</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2794,10 +2935,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D9">
         <v>-4</v>
@@ -2805,8 +2946,8 @@
       <c r="E9" t="s">
         <v>11</v>
       </c>
-      <c r="F9">
-        <v>0</v>
+      <c r="F9" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2814,19 +2955,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D10">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="F10" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2837,16 +2978,16 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D11">
         <v>-7</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -2856,18 +2997,21 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>88</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -2875,10 +3019,13 @@
         <v>8</v>
       </c>
       <c r="C2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -2886,87 +3033,111 @@
         <v>6</v>
       </c>
       <c r="C3">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6">
+        <v>-2</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
+      <c r="C7">
+        <v>-1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8">
+        <v>-1</v>
+      </c>
+      <c r="C8">
+        <v>-2</v>
+      </c>
+      <c r="D8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>-5</v>
+      </c>
+      <c r="C9">
+        <v>-4</v>
+      </c>
+      <c r="D9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7">
-        <v>-1</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>-2</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9">
+      <c r="B10">
         <v>-4</v>
       </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>-5</v>
-      </c>
       <c r="C10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>-6</v>
+      </c>
+      <c r="D10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
         <v>5</v>
       </c>
@@ -2974,7 +3145,10 @@
         <v>-7</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>-7</v>
+      </c>
+      <c r="D11" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Brown Munde 2026.xlsx
+++ b/data/leagues/Brown Munde 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="95">
   <si>
     <t>Still Rollin'</t>
   </si>
@@ -208,22 +208,22 @@
     <t>0-2</t>
   </si>
   <si>
-    <t>9.3-4.6-0.1</t>
-  </si>
-  <si>
-    <t>8.5-5.4-0.1</t>
-  </si>
-  <si>
-    <t>8.2-5.8-0.1</t>
-  </si>
-  <si>
-    <t>7.7-6.2-0.1</t>
-  </si>
-  <si>
-    <t>7.9-6.1-0.1</t>
-  </si>
-  <si>
-    <t>6.7-7.2-0.1</t>
+    <t>9.2-4.7-0.1</t>
+  </si>
+  <si>
+    <t>8.4-5.5-0.1</t>
+  </si>
+  <si>
+    <t>8.2-5.7-0.1</t>
+  </si>
+  <si>
+    <t>7.8-6.1-0.1</t>
+  </si>
+  <si>
+    <t>7.9-6.0-0.1</t>
+  </si>
+  <si>
+    <t>6.6-7.3-0.1</t>
   </si>
   <si>
     <t>6.5-7.4-0.1</t>
@@ -232,7 +232,7 @@
     <t>5.5-8.4-0.1</t>
   </si>
   <si>
-    <t>5.6-8.4-0.1</t>
+    <t>5.6-8.3-0.1</t>
   </si>
   <si>
     <t>3.8-10.1-0.1</t>
@@ -248,9 +248,6 @@
   </si>
   <si>
     <t>5-9</t>
-  </si>
-  <si>
-    <t>6-8</t>
   </si>
   <si>
     <t>4-10</t>
@@ -1065,25 +1062,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1572,37 +1569,37 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>44</v>
+        <v>41.1</v>
       </c>
       <c r="C2">
-        <v>22.2</v>
+        <v>22.8</v>
       </c>
       <c r="D2">
-        <v>13.4</v>
+        <v>13.1</v>
       </c>
       <c r="E2">
-        <v>7.9</v>
+        <v>11.1</v>
       </c>
       <c r="F2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="G2">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="H2">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="I2">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J2">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="K2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>97</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1610,37 +1607,37 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>15.7</v>
+        <v>15.4</v>
       </c>
       <c r="C3">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="D3">
-        <v>18.9</v>
+        <v>16.9</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>14.4</v>
       </c>
       <c r="F3">
-        <v>10.4</v>
+        <v>13.1</v>
       </c>
       <c r="G3">
-        <v>9.9</v>
+        <v>11.1</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>5.9</v>
       </c>
       <c r="I3">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="J3">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="K3">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="L3">
-        <v>87.40000000000001</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1648,37 +1645,37 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>15.3</v>
+        <v>17.2</v>
       </c>
       <c r="C4">
-        <v>19.4</v>
+        <v>19.7</v>
       </c>
       <c r="D4">
-        <v>17.2</v>
+        <v>15.7</v>
       </c>
       <c r="E4">
-        <v>13.6</v>
+        <v>14.2</v>
       </c>
       <c r="F4">
-        <v>12.3</v>
+        <v>12.9</v>
       </c>
       <c r="G4">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I4">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="J4">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="K4">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="L4">
-        <v>86.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1686,37 +1683,37 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="C5">
-        <v>11.5</v>
+        <v>12.2</v>
       </c>
       <c r="D5">
-        <v>16.1</v>
+        <v>16.9</v>
       </c>
       <c r="E5">
-        <v>20.2</v>
+        <v>17.6</v>
       </c>
       <c r="F5">
-        <v>17.2</v>
+        <v>16.8</v>
       </c>
       <c r="G5">
-        <v>12.6</v>
+        <v>12</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I5">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K5">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="L5">
-        <v>84</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1724,37 +1721,37 @@
         <v>1</v>
       </c>
       <c r="B6">
+        <v>13</v>
+      </c>
+      <c r="C6">
+        <v>15.9</v>
+      </c>
+      <c r="D6">
+        <v>18.5</v>
+      </c>
+      <c r="E6">
         <v>12.8</v>
       </c>
-      <c r="C6">
-        <v>15.5</v>
-      </c>
-      <c r="D6">
-        <v>15.4</v>
-      </c>
-      <c r="E6">
-        <v>16.1</v>
-      </c>
       <c r="F6">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="G6">
         <v>10.6</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="K6">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>82.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1762,37 +1759,37 @@
         <v>2</v>
       </c>
       <c r="B7">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="D7">
-        <v>8.300000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="E7">
         <v>9.1</v>
       </c>
       <c r="F7">
-        <v>14.3</v>
+        <v>13.2</v>
       </c>
       <c r="G7">
-        <v>14.8</v>
+        <v>15.7</v>
       </c>
       <c r="H7">
-        <v>15.3</v>
+        <v>15</v>
       </c>
       <c r="I7">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="J7">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K7">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>55.5</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1803,69 +1800,69 @@
         <v>1.5</v>
       </c>
       <c r="C8">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="D8">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="E8">
-        <v>10.6</v>
+        <v>11.5</v>
       </c>
       <c r="F8">
-        <v>14.2</v>
+        <v>11.9</v>
       </c>
       <c r="G8">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="H8">
-        <v>18.2</v>
+        <v>18.5</v>
       </c>
       <c r="I8">
-        <v>14.1</v>
+        <v>15.2</v>
       </c>
       <c r="J8">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="K8">
         <v>6.4</v>
       </c>
       <c r="L8">
-        <v>51.7</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B9">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="C9">
         <v>1.3</v>
       </c>
       <c r="D9">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="E9">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="G9">
-        <v>13.2</v>
+        <v>10.9</v>
       </c>
       <c r="H9">
-        <v>14.5</v>
+        <v>14.1</v>
       </c>
       <c r="I9">
-        <v>19.1</v>
+        <v>16.8</v>
       </c>
       <c r="J9">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="K9">
-        <v>17</v>
+        <v>19.9</v>
       </c>
       <c r="L9">
         <v>27.1</v>
@@ -1873,40 +1870,40 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B10">
         <v>0.5</v>
       </c>
       <c r="C10">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="D10">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="E10">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="F10">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="G10">
-        <v>8.4</v>
+        <v>10.9</v>
       </c>
       <c r="H10">
-        <v>14.1</v>
+        <v>15.1</v>
       </c>
       <c r="I10">
-        <v>20.5</v>
+        <v>22.5</v>
       </c>
       <c r="J10">
-        <v>24.9</v>
+        <v>22.7</v>
       </c>
       <c r="K10">
-        <v>16.1</v>
+        <v>13.6</v>
       </c>
       <c r="L10">
-        <v>24.4</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1914,7 +1911,7 @@
         <v>4</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C11">
         <v>0.1</v>
@@ -1923,28 +1920,28 @@
         <v>0.4</v>
       </c>
       <c r="E11">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="F11">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G11">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="H11">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I11">
-        <v>12.1</v>
+        <v>13.3</v>
       </c>
       <c r="J11">
-        <v>24.8</v>
+        <v>24.6</v>
       </c>
       <c r="K11">
-        <v>53</v>
+        <v>51.7</v>
       </c>
       <c r="L11">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
     </row>
   </sheetData>
@@ -1976,10 +1973,10 @@
         <v>100</v>
       </c>
       <c r="C2">
-        <v>96.89999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="D2">
-        <v>98</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1987,13 +1984,13 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>71.89999999999999</v>
+        <v>72</v>
       </c>
       <c r="C3">
-        <v>91.7</v>
+        <v>90.8</v>
       </c>
       <c r="D3">
-        <v>88.40000000000001</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2004,10 +2001,10 @@
         <v>100</v>
       </c>
       <c r="C4">
-        <v>89.60000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D4">
-        <v>85.7</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2015,13 +2012,13 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <v>36.2</v>
+        <v>41.09999999999999</v>
       </c>
       <c r="C5">
-        <v>87.09999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D5">
-        <v>83.09999999999999</v>
+        <v>83.59999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2029,13 +2026,13 @@
         <v>3</v>
       </c>
       <c r="B6">
-        <v>84.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="C6">
-        <v>89.90000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="D6">
-        <v>81.89999999999999</v>
+        <v>82.59999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2046,10 +2043,10 @@
         <v>100</v>
       </c>
       <c r="C7">
-        <v>47.2</v>
+        <v>55.8</v>
       </c>
       <c r="D7">
-        <v>56.89999999999999</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2057,13 +2054,13 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>8</v>
+        <v>6.3</v>
       </c>
       <c r="C8">
-        <v>46</v>
+        <v>46.9</v>
       </c>
       <c r="D8">
-        <v>50.6</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2071,13 +2068,13 @@
         <v>5</v>
       </c>
       <c r="B9">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="C9">
-        <v>27.8</v>
+        <v>22.9</v>
       </c>
       <c r="D9">
-        <v>26.8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2085,13 +2082,13 @@
         <v>0</v>
       </c>
       <c r="B10">
-        <v>90.40000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="C10">
-        <v>21.7</v>
+        <v>22.5</v>
       </c>
       <c r="D10">
-        <v>24.1</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2099,13 +2096,13 @@
         <v>4</v>
       </c>
       <c r="B11">
-        <v>8.799999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="C11">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="D11">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
     </row>
   </sheetData>
@@ -2490,10 +2487,10 @@
         <v>295.56</v>
       </c>
       <c r="F2">
-        <v>97</v>
+        <v>96.7</v>
       </c>
       <c r="G2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="s">
         <v>61</v>
@@ -2519,16 +2516,16 @@
         <v>243.38</v>
       </c>
       <c r="F3">
-        <v>87.40000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="G3">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="H3" t="s">
         <v>62</v>
       </c>
       <c r="I3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2548,10 +2545,10 @@
         <v>261.68</v>
       </c>
       <c r="F4">
-        <v>86.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G4">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H4" t="s">
         <v>63</v>
@@ -2577,10 +2574,10 @@
         <v>243.86</v>
       </c>
       <c r="F5">
-        <v>84</v>
+        <v>83.5</v>
       </c>
       <c r="G5">
-        <v>0.8999999999999999</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H5" t="s">
         <v>64</v>
@@ -2606,10 +2603,10 @@
         <v>257.82</v>
       </c>
       <c r="F6">
-        <v>82.39999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="G6">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="H6" t="s">
         <v>65</v>
@@ -2635,10 +2632,10 @@
         <v>218</v>
       </c>
       <c r="F7">
-        <v>55.50000000000001</v>
+        <v>52.8</v>
       </c>
       <c r="G7">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="H7" t="s">
         <v>66</v>
@@ -2664,7 +2661,7 @@
         <v>220.8</v>
       </c>
       <c r="F8">
-        <v>51.7</v>
+        <v>50.4</v>
       </c>
       <c r="G8">
         <v>6.4</v>
@@ -2678,7 +2675,7 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
         <v>58</v>
@@ -2687,16 +2684,16 @@
         <v>0.5</v>
       </c>
       <c r="D9">
-        <v>100.77</v>
+        <v>94.45</v>
       </c>
       <c r="E9">
-        <v>201.54</v>
+        <v>188.9</v>
       </c>
       <c r="F9">
         <v>27.1</v>
       </c>
       <c r="G9">
-        <v>17</v>
+        <v>19.9</v>
       </c>
       <c r="H9" t="s">
         <v>68</v>
@@ -2707,7 +2704,7 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B10" t="s">
         <v>58</v>
@@ -2716,22 +2713,22 @@
         <v>0.5</v>
       </c>
       <c r="D10">
-        <v>94.45</v>
+        <v>100.77</v>
       </c>
       <c r="E10">
-        <v>188.9</v>
+        <v>201.54</v>
       </c>
       <c r="F10">
-        <v>24.4</v>
+        <v>26.1</v>
       </c>
       <c r="G10">
-        <v>16.1</v>
+        <v>13.6</v>
       </c>
       <c r="H10" t="s">
         <v>69</v>
       </c>
       <c r="I10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2751,16 +2748,16 @@
         <v>198.64</v>
       </c>
       <c r="F11">
-        <v>4.100000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="G11">
-        <v>53</v>
+        <v>51.7</v>
       </c>
       <c r="H11" t="s">
         <v>70</v>
       </c>
       <c r="I11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -2778,16 +2775,16 @@
         <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2807,7 +2804,7 @@
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2827,7 +2824,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2847,7 +2844,7 @@
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2867,7 +2864,7 @@
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2887,7 +2884,7 @@
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2907,7 +2904,7 @@
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2927,7 +2924,7 @@
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2947,7 +2944,7 @@
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2967,7 +2964,7 @@
         <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2987,7 +2984,7 @@
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -3002,13 +2999,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -3022,7 +3019,7 @@
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3036,7 +3033,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3050,7 +3047,7 @@
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3064,7 +3061,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -3078,7 +3075,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -3092,7 +3089,7 @@
         <v>-1</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -3106,7 +3103,7 @@
         <v>-2</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -3120,7 +3117,7 @@
         <v>-4</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -3134,7 +3131,7 @@
         <v>-6</v>
       </c>
       <c r="D10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -3148,7 +3145,7 @@
         <v>-7</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Brown Munde 2026.xlsx
+++ b/data/leagues/Brown Munde 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="100">
   <si>
     <t>Still Rollin'</t>
   </si>
@@ -55,13 +55,16 @@
     <t>BurgerBoyz</t>
   </si>
   <si>
-    <t>1-1-0</t>
-  </si>
-  <si>
-    <t>2-0-0</t>
-  </si>
-  <si>
-    <t>0-2-0</t>
+    <t>2-1-0</t>
+  </si>
+  <si>
+    <t>3-0-0</t>
+  </si>
+  <si>
+    <t>1-2-0</t>
+  </si>
+  <si>
+    <t>0-3-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -124,6 +127,9 @@
     <t>Week_3</t>
   </si>
   <si>
+    <t>Week_4</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -145,33 +151,33 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Prahlad Singh</t>
+  </si>
+  <si>
+    <t>KASHYAP AShok</t>
+  </si>
+  <si>
+    <t>Krishna Padodara</t>
+  </si>
+  <si>
     <t>Utkarsh Gupta</t>
   </si>
   <si>
+    <t>Harshit Aggarwal</t>
+  </si>
+  <si>
+    <t>suraj bhalani</t>
+  </si>
+  <si>
+    <t>Kiran MADUGULA</t>
+  </si>
+  <si>
     <t>Hark Nanda</t>
   </si>
   <si>
-    <t>suraj bhalani</t>
-  </si>
-  <si>
-    <t>Krishna Padodara</t>
-  </si>
-  <si>
-    <t>KASHYAP AShok</t>
-  </si>
-  <si>
     <t>Pawan Bhambhwani</t>
   </si>
   <si>
-    <t>Prahlad Singh</t>
-  </si>
-  <si>
-    <t>Kiran MADUGULA</t>
-  </si>
-  <si>
-    <t>Harshit Aggarwal</t>
-  </si>
-  <si>
     <t>Guruansh Singh</t>
   </si>
   <si>
@@ -199,43 +205,43 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>2-0</t>
-  </si>
-  <si>
-    <t>0-2</t>
-  </si>
-  <si>
-    <t>9.2-4.7-0.1</t>
-  </si>
-  <si>
-    <t>8.4-5.5-0.1</t>
-  </si>
-  <si>
-    <t>8.2-5.7-0.1</t>
-  </si>
-  <si>
-    <t>7.8-6.1-0.1</t>
-  </si>
-  <si>
-    <t>7.9-6.0-0.1</t>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>3-0</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>8.9-5.0-0.1</t>
+  </si>
+  <si>
+    <t>9.0-4.9-0.1</t>
+  </si>
+  <si>
+    <t>8.7-5.2-0.1</t>
+  </si>
+  <si>
+    <t>7.2-6.7-0.1</t>
+  </si>
+  <si>
+    <t>6.8-7.1-0.1</t>
+  </si>
+  <si>
+    <t>6.7-7.2-0.1</t>
   </si>
   <si>
     <t>6.6-7.3-0.1</t>
   </si>
   <si>
-    <t>6.5-7.4-0.1</t>
-  </si>
-  <si>
-    <t>5.5-8.4-0.1</t>
-  </si>
-  <si>
-    <t>5.6-8.3-0.1</t>
-  </si>
-  <si>
-    <t>3.8-10.1-0.1</t>
+    <t>5.4-8.5-0.1</t>
+  </si>
+  <si>
+    <t>5.0-8.9-0.1</t>
+  </si>
+  <si>
+    <t>5.1-8.8-0.1</t>
   </si>
   <si>
     <t>9-5</t>
@@ -250,9 +256,6 @@
     <t>5-9</t>
   </si>
   <si>
-    <t>4-10</t>
-  </si>
-  <si>
     <t>Owners</t>
   </si>
   <si>
@@ -265,28 +268,40 @@
     <t>↑2</t>
   </si>
   <si>
+    <t>↑11</t>
+  </si>
+  <si>
     <t>0</t>
   </si>
   <si>
-    <t>↑1</t>
+    <t>↑8</t>
+  </si>
+  <si>
+    <t>↑3</t>
+  </si>
+  <si>
+    <t>↑5</t>
   </si>
   <si>
     <t>↓3</t>
   </si>
   <si>
-    <t>↑3</t>
-  </si>
-  <si>
-    <t>↓1</t>
-  </si>
-  <si>
-    <t>↓2</t>
+    <t>↓6</t>
+  </si>
+  <si>
+    <t>↓11</t>
+  </si>
+  <si>
+    <t>↓9</t>
   </si>
   <si>
     <t>Week 1</t>
   </si>
   <si>
     <t>Week 2</t>
+  </si>
+  <si>
+    <t>Week 3</t>
   </si>
   <si>
     <t>Week</t>
@@ -708,31 +723,31 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H2" t="s">
         <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -743,31 +758,31 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H3" t="s">
         <v>10</v>
       </c>
       <c r="I3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -816,16 +831,16 @@
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H5" t="s">
         <v>10</v>
@@ -834,10 +849,10 @@
         <v>10</v>
       </c>
       <c r="J5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -851,7 +866,7 @@
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
         <v>12</v>
@@ -860,7 +875,7 @@
         <v>12</v>
       </c>
       <c r="G6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H6" t="s">
         <v>12</v>
@@ -886,7 +901,7 @@
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -895,7 +910,7 @@
         <v>10</v>
       </c>
       <c r="G7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H7" t="s">
         <v>10</v>
@@ -915,34 +930,34 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -956,16 +971,16 @@
         <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H9" t="s">
         <v>10</v>
@@ -974,10 +989,10 @@
         <v>10</v>
       </c>
       <c r="J9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -991,16 +1006,16 @@
         <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H10" t="s">
         <v>10</v>
@@ -1009,7 +1024,7 @@
         <v>10</v>
       </c>
       <c r="J10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K10" t="s">
         <v>11</v>
@@ -1026,7 +1041,7 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -1035,7 +1050,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H11" t="s">
         <v>11</v>
@@ -1044,7 +1059,7 @@
         <v>10</v>
       </c>
       <c r="J11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K11" t="s">
         <v>11</v>
@@ -1057,30 +1072,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1088,25 +1103,25 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
       <c r="E2">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1117,22 +1132,22 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3">
-        <v>-7</v>
+        <v>10</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1143,22 +1158,100 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <v>-7</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>8</v>
+      </c>
+      <c r="H4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
         <v>9</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5">
+        <v>-1</v>
+      </c>
+      <c r="G5">
+        <v>7</v>
+      </c>
+      <c r="H5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
         <v>0</v>
       </c>
-      <c r="E4">
+      <c r="E6">
         <v>-4</v>
       </c>
-      <c r="F4">
+      <c r="F6">
         <v>-2</v>
       </c>
-      <c r="G4">
+      <c r="G6">
         <v>2</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H6" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <v>-11</v>
+      </c>
+      <c r="F7">
+        <v>-10</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7" t="s">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1173,13 +1266,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1190,10 +1283,10 @@
         <v>8</v>
       </c>
       <c r="C2">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1201,10 +1294,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1215,13 +1308,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1229,13 +1322,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1243,13 +1336,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1257,13 +1350,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1271,10 +1364,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -1288,10 +1381,10 @@
         <v>1</v>
       </c>
       <c r="C9">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1299,13 +1392,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1316,7 +1409,7 @@
         <v>9</v>
       </c>
       <c r="C11">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
@@ -1334,16 +1427,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1354,10 +1447,10 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="D2">
-        <v>-0.6000000000000001</v>
+        <v>-0.8999999999999999</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
@@ -1371,13 +1464,13 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="D3">
-        <v>0.3999999999999999</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1385,13 +1478,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="D4">
-        <v>0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -1405,13 +1498,13 @@
         <v>3</v>
       </c>
       <c r="C5">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="D5">
-        <v>0.2</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1419,16 +1512,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="D6">
-        <v>0.1000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1436,16 +1529,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="D7">
-        <v>-0.09999999999999998</v>
+        <v>0.5</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1453,13 +1546,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="D8">
-        <v>-0.2</v>
+        <v>-0.7</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -1470,16 +1563,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="D9">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1487,16 +1580,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="D10">
-        <v>-0.3</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1504,16 +1597,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="D11">
-        <v>0.5</v>
+        <v>-1.1</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1528,40 +1621,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1569,34 +1662,34 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>41.1</v>
+        <v>35.9</v>
       </c>
       <c r="C2">
-        <v>22.8</v>
+        <v>23.3</v>
       </c>
       <c r="D2">
-        <v>13.1</v>
+        <v>17.1</v>
       </c>
       <c r="E2">
-        <v>11.1</v>
+        <v>10.2</v>
       </c>
       <c r="F2">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="G2">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="H2">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="I2">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J2">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L2">
         <v>96.7</v>
@@ -1607,189 +1700,189 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>15.4</v>
+        <v>25.5</v>
       </c>
       <c r="C3">
-        <v>17.5</v>
+        <v>23.9</v>
       </c>
       <c r="D3">
-        <v>16.9</v>
+        <v>20.9</v>
       </c>
       <c r="E3">
-        <v>14.4</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>13.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G3">
-        <v>11.1</v>
+        <v>3.6</v>
       </c>
       <c r="H3">
-        <v>5.9</v>
+        <v>3.6</v>
       </c>
       <c r="I3">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J3">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="K3">
         <v>0.3</v>
       </c>
       <c r="L3">
-        <v>88.40000000000001</v>
+        <v>94.2</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B4">
-        <v>17.2</v>
+        <v>25</v>
       </c>
       <c r="C4">
-        <v>19.7</v>
+        <v>24.4</v>
       </c>
       <c r="D4">
-        <v>15.7</v>
+        <v>17.1</v>
       </c>
       <c r="E4">
-        <v>14.2</v>
+        <v>12.6</v>
       </c>
       <c r="F4">
-        <v>12.9</v>
+        <v>9.1</v>
       </c>
       <c r="G4">
-        <v>8.199999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="H4">
-        <v>6.2</v>
+        <v>3.1</v>
       </c>
       <c r="I4">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="J4">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="L4">
-        <v>87.90000000000001</v>
+        <v>93.59999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B5">
-        <v>8</v>
+        <v>5.9</v>
       </c>
       <c r="C5">
-        <v>12.2</v>
+        <v>10.5</v>
       </c>
       <c r="D5">
-        <v>16.9</v>
+        <v>14.2</v>
       </c>
       <c r="E5">
-        <v>17.6</v>
+        <v>15.5</v>
       </c>
       <c r="F5">
-        <v>16.8</v>
+        <v>15.3</v>
       </c>
       <c r="G5">
-        <v>12</v>
+        <v>14.7</v>
       </c>
       <c r="H5">
-        <v>8.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I5">
-        <v>5.5</v>
+        <v>7.7</v>
       </c>
       <c r="J5">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="L5">
-        <v>83.5</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>13</v>
+        <v>2.7</v>
       </c>
       <c r="C6">
-        <v>15.9</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>18.5</v>
+        <v>9.1</v>
       </c>
       <c r="E6">
-        <v>12.8</v>
+        <v>16.5</v>
       </c>
       <c r="F6">
-        <v>11.8</v>
+        <v>14.5</v>
       </c>
       <c r="G6">
-        <v>10.6</v>
+        <v>16.4</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>10.2</v>
       </c>
       <c r="J6">
-        <v>2.1</v>
+        <v>6.8</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="L6">
-        <v>82.59999999999999</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7">
         <v>2</v>
       </c>
-      <c r="B7">
-        <v>2.8</v>
-      </c>
       <c r="C7">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="D7">
-        <v>6.7</v>
+        <v>9.6</v>
       </c>
       <c r="E7">
+        <v>14.1</v>
+      </c>
+      <c r="F7">
+        <v>16.8</v>
+      </c>
+      <c r="G7">
+        <v>14.5</v>
+      </c>
+      <c r="H7">
+        <v>13.1</v>
+      </c>
+      <c r="I7">
+        <v>11.6</v>
+      </c>
+      <c r="J7">
         <v>9.1</v>
       </c>
-      <c r="F7">
-        <v>13.2</v>
-      </c>
-      <c r="G7">
-        <v>15.7</v>
-      </c>
-      <c r="H7">
-        <v>15</v>
-      </c>
-      <c r="I7">
-        <v>13.2</v>
-      </c>
-      <c r="J7">
-        <v>13</v>
-      </c>
       <c r="K7">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="L7">
-        <v>52.8</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1797,113 +1890,113 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="C8">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="D8">
-        <v>5.9</v>
+        <v>7.3</v>
       </c>
       <c r="E8">
-        <v>11.5</v>
+        <v>10.6</v>
       </c>
       <c r="F8">
-        <v>11.9</v>
+        <v>13.1</v>
       </c>
       <c r="G8">
-        <v>15.5</v>
+        <v>15.8</v>
       </c>
       <c r="H8">
-        <v>18.5</v>
+        <v>15.2</v>
       </c>
       <c r="I8">
-        <v>15.2</v>
+        <v>13.5</v>
       </c>
       <c r="J8">
-        <v>9.5</v>
+        <v>11.8</v>
       </c>
       <c r="K8">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="L8">
-        <v>50.4</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B9">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="C9">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="D9">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="E9">
+        <v>3.6</v>
+      </c>
+      <c r="F9">
         <v>4.8</v>
       </c>
-      <c r="F9">
-        <v>6.8</v>
-      </c>
       <c r="G9">
-        <v>10.9</v>
+        <v>9.4</v>
       </c>
       <c r="H9">
-        <v>14.1</v>
+        <v>14.5</v>
       </c>
       <c r="I9">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
       <c r="J9">
-        <v>22.1</v>
+        <v>22.5</v>
       </c>
       <c r="K9">
-        <v>19.9</v>
+        <v>25.6</v>
       </c>
       <c r="L9">
-        <v>27.1</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10">
         <v>0</v>
       </c>
-      <c r="B10">
-        <v>0.5</v>
-      </c>
       <c r="C10">
+        <v>0.8</v>
+      </c>
+      <c r="D10">
         <v>1.1</v>
       </c>
-      <c r="D10">
-        <v>3</v>
-      </c>
       <c r="E10">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="F10">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="G10">
-        <v>10.9</v>
+        <v>8.6</v>
       </c>
       <c r="H10">
-        <v>15.1</v>
+        <v>12.2</v>
       </c>
       <c r="I10">
-        <v>22.5</v>
+        <v>17.5</v>
       </c>
       <c r="J10">
-        <v>22.7</v>
+        <v>20.3</v>
       </c>
       <c r="K10">
-        <v>13.6</v>
+        <v>31.3</v>
       </c>
       <c r="L10">
-        <v>26.1</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1911,37 +2004,37 @@
         <v>4</v>
       </c>
       <c r="B11">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="C11">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="D11">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="E11">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="F11">
-        <v>0.9</v>
+        <v>6.5</v>
       </c>
       <c r="G11">
-        <v>2.6</v>
+        <v>7.4</v>
       </c>
       <c r="H11">
-        <v>5.9</v>
+        <v>12.2</v>
       </c>
       <c r="I11">
-        <v>13.3</v>
+        <v>18.7</v>
       </c>
       <c r="J11">
-        <v>24.6</v>
+        <v>23.7</v>
       </c>
       <c r="K11">
-        <v>51.7</v>
+        <v>27.2</v>
       </c>
       <c r="L11">
-        <v>4.5</v>
+        <v>18.2</v>
       </c>
     </row>
   </sheetData>
@@ -1951,21 +2044,24 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -1973,136 +2069,166 @@
         <v>100</v>
       </c>
       <c r="C2">
-        <v>97.2</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D2">
-        <v>96.8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>97.39999999999999</v>
+      </c>
+      <c r="E2">
+        <v>97.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B3">
-        <v>72</v>
+        <v>73.5</v>
       </c>
       <c r="C3">
-        <v>90.8</v>
+        <v>96.2</v>
       </c>
       <c r="D3">
-        <v>89.3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="E3">
+        <v>94.59999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B4">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="C4">
-        <v>87.09999999999999</v>
+        <v>50</v>
       </c>
       <c r="D4">
-        <v>89.2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>95.5</v>
+      </c>
+      <c r="E4">
+        <v>92.60000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B5">
-        <v>41.09999999999999</v>
+        <v>37.1</v>
       </c>
       <c r="C5">
-        <v>83.59999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="D5">
-        <v>83.59999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>78.8</v>
+      </c>
+      <c r="E5">
+        <v>73.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>100</v>
+      </c>
+      <c r="C6">
+        <v>96.8</v>
+      </c>
+      <c r="D6">
+        <v>68.8</v>
+      </c>
+      <c r="E6">
+        <v>66.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B6">
-        <v>81.5</v>
-      </c>
-      <c r="C6">
+      <c r="B7">
+        <v>80.2</v>
+      </c>
+      <c r="C7">
         <v>90.7</v>
       </c>
-      <c r="D6">
-        <v>82.59999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7">
-        <v>100</v>
-      </c>
-      <c r="C7">
-        <v>55.8</v>
-      </c>
       <c r="D7">
-        <v>54.3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>63.5</v>
+      </c>
+      <c r="E7">
+        <v>65.60000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>6.3</v>
+        <v>8.200000000000001</v>
       </c>
       <c r="C8">
-        <v>46.9</v>
+        <v>40.7</v>
       </c>
       <c r="D8">
-        <v>47.4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>53.40000000000001</v>
+      </c>
+      <c r="E8">
+        <v>53.90000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9">
+        <v>88.2</v>
+      </c>
+      <c r="C9">
+        <v>16.4</v>
+      </c>
+      <c r="D9">
+        <v>17.7</v>
+      </c>
+      <c r="E9">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10">
+        <v>12.7</v>
+      </c>
+      <c r="C10">
+        <v>4.6</v>
+      </c>
+      <c r="D10">
+        <v>13.7</v>
+      </c>
+      <c r="E10">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B9">
-        <v>0.3</v>
-      </c>
-      <c r="C9">
-        <v>22.9</v>
-      </c>
-      <c r="D9">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10">
-        <v>89.3</v>
-      </c>
-      <c r="C10">
-        <v>22.5</v>
-      </c>
-      <c r="D10">
-        <v>24.7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="B11">
-        <v>9.5</v>
+        <v>0.2</v>
       </c>
       <c r="C11">
-        <v>2.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D11">
-        <v>5.1</v>
+        <v>16.1</v>
+      </c>
+      <c r="E11">
+        <v>15.3</v>
       </c>
     </row>
   </sheetData>
@@ -2117,28 +2243,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2146,28 +2272,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D2">
-        <v>121.69</v>
+        <v>100.86</v>
       </c>
       <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2">
+        <v>116.33</v>
+      </c>
+      <c r="G2">
+        <v>0.485</v>
+      </c>
+      <c r="H2">
+        <v>1.8</v>
+      </c>
+      <c r="I2">
         <v>11</v>
-      </c>
-      <c r="F2">
-        <v>117.7</v>
-      </c>
-      <c r="G2">
-        <v>0.417</v>
-      </c>
-      <c r="H2">
-        <v>1.2</v>
-      </c>
-      <c r="I2">
-        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2175,28 +2301,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D3">
-        <v>99.31999999999999</v>
+        <v>121</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
       </c>
       <c r="F3">
-        <v>119.67</v>
+        <v>115.42</v>
       </c>
       <c r="G3">
-        <v>0.583</v>
+        <v>0.485</v>
       </c>
       <c r="H3">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="I3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2204,28 +2330,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D4">
-        <v>94.45</v>
+        <v>117</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>118.25</v>
+        <v>114.56</v>
       </c>
       <c r="G4">
-        <v>0.5</v>
+        <v>0.515</v>
       </c>
       <c r="H4">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="I4">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2233,28 +2359,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D5">
-        <v>130.84</v>
+        <v>119.33</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>113.95</v>
+        <v>115.72</v>
       </c>
       <c r="G5">
-        <v>0.5</v>
+        <v>0.424</v>
       </c>
       <c r="H5">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="I5">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2262,28 +2388,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D6">
-        <v>128.91</v>
+        <v>116.77</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>115.73</v>
+        <v>115.98</v>
       </c>
       <c r="G6">
-        <v>0.5</v>
+        <v>0.515</v>
       </c>
       <c r="H6">
-        <v>0.2</v>
+        <v>-0.5</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2291,28 +2417,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D7">
-        <v>109</v>
+        <v>103.31</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>114.44</v>
+        <v>116.19</v>
       </c>
       <c r="G7">
-        <v>0.5</v>
+        <v>0.515</v>
       </c>
       <c r="H7">
-        <v>-0.2</v>
+        <v>-0.6</v>
       </c>
       <c r="I7">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2320,28 +2446,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D8">
-        <v>100.77</v>
+        <v>108.81</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
       <c r="F8">
-        <v>116.96</v>
+        <v>114.83</v>
       </c>
       <c r="G8">
-        <v>0.458</v>
+        <v>0.455</v>
       </c>
       <c r="H8">
-        <v>-0.3</v>
+        <v>-0.6</v>
       </c>
       <c r="I8">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2349,28 +2475,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D9">
-        <v>110.4</v>
+        <v>104.87</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F9">
-        <v>117.41</v>
+        <v>115.18</v>
       </c>
       <c r="G9">
-        <v>0.5</v>
+        <v>0.576</v>
       </c>
       <c r="H9">
-        <v>-0.4</v>
+        <v>-1</v>
       </c>
       <c r="I9">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2378,28 +2504,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D10">
-        <v>121.93</v>
+        <v>123.97</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
       </c>
       <c r="F10">
-        <v>117.06</v>
+        <v>113.21</v>
       </c>
       <c r="G10">
-        <v>0.542</v>
+        <v>0.485</v>
       </c>
       <c r="H10">
-        <v>-0.8</v>
+        <v>-1.4</v>
       </c>
       <c r="I10">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2410,25 +2536,25 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D11">
-        <v>147.78</v>
+        <v>135.7</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F11">
-        <v>113.94</v>
+        <v>114.21</v>
       </c>
       <c r="G11">
-        <v>0.5</v>
+        <v>0.545</v>
       </c>
       <c r="H11">
         <v>-1.5</v>
       </c>
       <c r="I11">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -2443,31 +2569,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2475,28 +2601,28 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C2">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D2">
-        <v>147.78</v>
+        <v>135.7</v>
       </c>
       <c r="E2">
-        <v>295.56</v>
+        <v>407.1</v>
       </c>
       <c r="F2">
         <v>96.7</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2504,144 +2630,144 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>121.69</v>
+        <v>119.3333333333333</v>
       </c>
       <c r="E3">
-        <v>243.38</v>
+        <v>358</v>
       </c>
       <c r="F3">
-        <v>88.40000000000001</v>
+        <v>94.19999999999999</v>
       </c>
       <c r="G3">
         <v>0.3</v>
       </c>
       <c r="H3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C4">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D4">
-        <v>130.84</v>
+        <v>123.9666666666667</v>
       </c>
       <c r="E4">
-        <v>261.68</v>
+        <v>371.9</v>
       </c>
       <c r="F4">
-        <v>87.90000000000001</v>
+        <v>93.60000000000001</v>
       </c>
       <c r="G4">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="H4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C5">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D5">
-        <v>121.93</v>
+        <v>121</v>
       </c>
       <c r="E5">
-        <v>243.86</v>
+        <v>363</v>
       </c>
       <c r="F5">
-        <v>83.5</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="G5">
-        <v>0.7000000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="H5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D6">
-        <v>128.91</v>
+        <v>117</v>
       </c>
       <c r="E6">
-        <v>257.82</v>
+        <v>351</v>
       </c>
       <c r="F6">
-        <v>82.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="H6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D7">
-        <v>109</v>
+        <v>116.7666666666667</v>
       </c>
       <c r="E7">
-        <v>218</v>
+        <v>350.3</v>
       </c>
       <c r="F7">
-        <v>52.8</v>
+        <v>62.6</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="H7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2649,86 +2775,86 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D8">
-        <v>110.4</v>
+        <v>108.8133333333333</v>
       </c>
       <c r="E8">
-        <v>220.8</v>
+        <v>326.44</v>
       </c>
       <c r="F8">
-        <v>50.4</v>
+        <v>53.5</v>
       </c>
       <c r="G8">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C9">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D9">
-        <v>94.45</v>
+        <v>100.86</v>
       </c>
       <c r="E9">
-        <v>188.9</v>
+        <v>302.58</v>
       </c>
       <c r="F9">
-        <v>27.1</v>
+        <v>21.2</v>
       </c>
       <c r="G9">
-        <v>19.9</v>
+        <v>25.6</v>
       </c>
       <c r="H9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C10">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D10">
-        <v>100.77</v>
+        <v>103.3133333333333</v>
       </c>
       <c r="E10">
-        <v>201.54</v>
+        <v>309.94</v>
       </c>
       <c r="F10">
-        <v>26.1</v>
+        <v>18.7</v>
       </c>
       <c r="G10">
-        <v>13.6</v>
+        <v>31.3</v>
       </c>
       <c r="H10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2739,25 +2865,25 @@
         <v>60</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D11">
-        <v>99.31999999999999</v>
+        <v>104.8733333333333</v>
       </c>
       <c r="E11">
-        <v>198.64</v>
+        <v>314.62</v>
       </c>
       <c r="F11">
-        <v>4.5</v>
+        <v>18.2</v>
       </c>
       <c r="G11">
-        <v>51.7</v>
+        <v>27.2</v>
       </c>
       <c r="H11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2772,19 +2898,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2795,16 +2921,16 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2812,19 +2938,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2832,19 +2958,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2852,19 +2978,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2872,19 +2998,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2892,19 +3018,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D7">
         <v>-1</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2912,10 +3038,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D8">
         <v>-2</v>
@@ -2924,7 +3050,7 @@
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2932,19 +3058,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D9">
         <v>-4</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2952,19 +3078,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D10">
-        <v>-6</v>
+        <v>-10</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2972,19 +3098,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C11" t="s">
         <v>42</v>
       </c>
       <c r="D11">
-        <v>-7</v>
+        <v>-11</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -2994,21 +3120,24 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>92</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -3018,134 +3147,164 @@
       <c r="C2">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="D2">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>-1</v>
+      </c>
+      <c r="D3">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
+      <c r="B4">
         <v>6</v>
       </c>
-      <c r="C3">
+      <c r="C4">
         <v>6</v>
       </c>
-      <c r="D3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>-7</v>
+      </c>
+      <c r="C5">
+        <v>-7</v>
+      </c>
+      <c r="D5">
         <v>1</v>
       </c>
-      <c r="B4">
+      <c r="E5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>-5</v>
+      </c>
+      <c r="C6">
+        <v>-4</v>
+      </c>
+      <c r="D6">
+        <v>-1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>-4</v>
+      </c>
+      <c r="C7">
+        <v>-6</v>
+      </c>
+      <c r="D7">
+        <v>-1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>-2</v>
+      </c>
+      <c r="C8">
         <v>1</v>
       </c>
-      <c r="C4">
+      <c r="D8">
+        <v>-2</v>
+      </c>
+      <c r="E8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
         <v>2</v>
       </c>
-      <c r="D4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
+      <c r="D9">
+        <v>-4</v>
+      </c>
+      <c r="E9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5">
+      <c r="B10">
         <v>4</v>
       </c>
-      <c r="C5">
+      <c r="C10">
         <v>1</v>
       </c>
-      <c r="D5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6">
+      <c r="D10">
+        <v>-10</v>
+      </c>
+      <c r="E10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11">
+        <v>-1</v>
+      </c>
+      <c r="C11">
         <v>-2</v>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>-1</v>
-      </c>
-      <c r="D7" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8">
-        <v>-1</v>
-      </c>
-      <c r="C8">
-        <v>-2</v>
-      </c>
-      <c r="D8" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>-5</v>
-      </c>
-      <c r="C9">
-        <v>-4</v>
-      </c>
-      <c r="D9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10">
-        <v>-4</v>
-      </c>
-      <c r="C10">
-        <v>-6</v>
-      </c>
-      <c r="D10" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11">
-        <v>-7</v>
-      </c>
-      <c r="C11">
-        <v>-7</v>
-      </c>
-      <c r="D11" t="s">
-        <v>80</v>
+      <c r="D11">
+        <v>-11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Brown Munde 2026.xlsx
+++ b/data/leagues/Brown Munde 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="104">
   <si>
     <t>Still Rollin'</t>
   </si>
@@ -55,16 +55,19 @@
     <t>BurgerBoyz</t>
   </si>
   <si>
-    <t>2-1-0</t>
-  </si>
-  <si>
-    <t>3-0-0</t>
-  </si>
-  <si>
-    <t>1-2-0</t>
-  </si>
-  <si>
-    <t>0-3-0</t>
+    <t>2-2-0</t>
+  </si>
+  <si>
+    <t>3-1-0</t>
+  </si>
+  <si>
+    <t>1-3-0</t>
+  </si>
+  <si>
+    <t>4-0-0</t>
+  </si>
+  <si>
+    <t>0-4-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -130,6 +133,9 @@
     <t>Week_4</t>
   </si>
   <si>
+    <t>Week_5</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -151,36 +157,36 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>KASHYAP AShok</t>
+  </si>
+  <si>
     <t>Prahlad Singh</t>
   </si>
   <si>
-    <t>KASHYAP AShok</t>
+    <t>Utkarsh Gupta</t>
   </si>
   <si>
     <t>Krishna Padodara</t>
   </si>
   <si>
-    <t>Utkarsh Gupta</t>
+    <t>Pawan Bhambhwani</t>
   </si>
   <si>
     <t>Harshit Aggarwal</t>
   </si>
   <si>
+    <t>Kiran MADUGULA</t>
+  </si>
+  <si>
+    <t>Hark Nanda</t>
+  </si>
+  <si>
+    <t>Guruansh Singh</t>
+  </si>
+  <si>
     <t>suraj bhalani</t>
   </si>
   <si>
-    <t>Kiran MADUGULA</t>
-  </si>
-  <si>
-    <t>Hark Nanda</t>
-  </si>
-  <si>
-    <t>Pawan Bhambhwani</t>
-  </si>
-  <si>
-    <t>Guruansh Singh</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -205,43 +211,46 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>3-0</t>
-  </si>
-  <si>
-    <t>2-1</t>
+    <t>4-0</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>9.8-4.1-0.1</t>
+  </si>
+  <si>
+    <t>8.7-5.2-0.1</t>
   </si>
   <si>
     <t>8.9-5.0-0.1</t>
   </si>
   <si>
-    <t>9.0-4.9-0.1</t>
-  </si>
-  <si>
-    <t>8.7-5.2-0.1</t>
-  </si>
-  <si>
-    <t>7.2-6.7-0.1</t>
-  </si>
-  <si>
-    <t>6.8-7.1-0.1</t>
-  </si>
-  <si>
-    <t>6.7-7.2-0.1</t>
-  </si>
-  <si>
-    <t>6.6-7.3-0.1</t>
-  </si>
-  <si>
-    <t>5.4-8.5-0.1</t>
-  </si>
-  <si>
-    <t>5.0-8.9-0.1</t>
-  </si>
-  <si>
-    <t>5.1-8.8-0.1</t>
+    <t>7.9-5.9-0.1</t>
+  </si>
+  <si>
+    <t>6.4-7.5-0.1</t>
+  </si>
+  <si>
+    <t>5.7-8.2-0.1</t>
+  </si>
+  <si>
+    <t>5.2-8.7-0.1</t>
+  </si>
+  <si>
+    <t>4.2-9.7-0.1</t>
+  </si>
+  <si>
+    <t>4.0-9.9-0.1</t>
+  </si>
+  <si>
+    <t>10-4</t>
   </si>
   <si>
     <t>9-5</t>
@@ -250,12 +259,15 @@
     <t>8-6</t>
   </si>
   <si>
-    <t>7-7</t>
+    <t>6-8</t>
   </si>
   <si>
     <t>5-9</t>
   </si>
   <si>
+    <t>4-10</t>
+  </si>
+  <si>
     <t>Owners</t>
   </si>
   <si>
@@ -265,34 +277,31 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↑2</t>
-  </si>
-  <si>
-    <t>↑11</t>
+    <t>↑6</t>
+  </si>
+  <si>
+    <t>↑1</t>
+  </si>
+  <si>
+    <t>↓5</t>
+  </si>
+  <si>
+    <t>↑3</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>↑8</t>
-  </si>
-  <si>
-    <t>↑3</t>
-  </si>
-  <si>
-    <t>↑5</t>
-  </si>
-  <si>
     <t>↓3</t>
   </si>
   <si>
-    <t>↓6</t>
-  </si>
-  <si>
-    <t>↓11</t>
-  </si>
-  <si>
-    <t>↓9</t>
+    <t>↑4</t>
+  </si>
+  <si>
+    <t>↓7</t>
+  </si>
+  <si>
+    <t>↓1</t>
   </si>
   <si>
     <t>Week 1</t>
@@ -302,6 +311,9 @@
   </si>
   <si>
     <t>Week 3</t>
+  </si>
+  <si>
+    <t>Week 4</t>
   </si>
   <si>
     <t>Week</t>
@@ -729,7 +741,7 @@
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
         <v>12</v>
@@ -741,13 +753,13 @@
         <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -790,16 +802,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
         <v>10</v>
@@ -811,13 +823,13 @@
         <v>10</v>
       </c>
       <c r="I4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -825,34 +837,34 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5" t="s">
         <v>10</v>
       </c>
       <c r="H5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -884,7 +896,7 @@
         <v>12</v>
       </c>
       <c r="J6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K6" t="s">
         <v>11</v>
@@ -901,7 +913,7 @@
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -919,10 +931,10 @@
         <v>10</v>
       </c>
       <c r="J7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -933,13 +945,13 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
@@ -951,13 +963,13 @@
         <v>12</v>
       </c>
       <c r="I8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -965,34 +977,34 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1003,10 +1015,10 @@
         <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -1021,13 +1033,13 @@
         <v>10</v>
       </c>
       <c r="I10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1035,19 +1047,19 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G11" t="s">
         <v>10</v>
@@ -1056,13 +1068,13 @@
         <v>11</v>
       </c>
       <c r="I11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1072,30 +1084,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1252,6 +1264,32 @@
       </c>
       <c r="H7" t="s">
         <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1266,13 +1304,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1280,13 +1318,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1294,13 +1332,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1308,13 +1346,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1325,7 +1363,7 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
@@ -1336,13 +1374,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1350,13 +1388,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1367,7 +1405,7 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -1378,13 +1416,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1392,10 +1430,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
@@ -1409,10 +1447,10 @@
         <v>9</v>
       </c>
       <c r="C11">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1427,16 +1465,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1447,13 +1485,13 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="D2">
-        <v>-0.8999999999999999</v>
+        <v>-1.1</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1461,16 +1499,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="D3">
-        <v>0.8999999999999999</v>
+        <v>-0.5</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1478,13 +1516,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="D4">
-        <v>-0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -1495,16 +1533,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C5">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="D5">
-        <v>0.6000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1512,16 +1550,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="D6">
-        <v>0.5</v>
+        <v>-0.7000000000000002</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1532,10 +1570,10 @@
         <v>5</v>
       </c>
       <c r="C7">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="D7">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
@@ -1546,16 +1584,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="D8">
-        <v>-0.7</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1563,13 +1601,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="D9">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
@@ -1580,13 +1618,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="D10">
-        <v>0.1000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
@@ -1600,10 +1638,10 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="D11">
-        <v>-1.1</v>
+        <v>-0.8</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -1621,116 +1659,116 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2">
-        <v>35.9</v>
+        <v>36.5</v>
       </c>
       <c r="C2">
-        <v>23.3</v>
+        <v>24.2</v>
       </c>
       <c r="D2">
-        <v>17.1</v>
+        <v>16.5</v>
       </c>
       <c r="E2">
-        <v>10.2</v>
+        <v>12.5</v>
       </c>
       <c r="F2">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="G2">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="H2">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>96.7</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3">
-        <v>25.5</v>
+        <v>21.9</v>
       </c>
       <c r="C3">
-        <v>23.9</v>
+        <v>20.7</v>
       </c>
       <c r="D3">
-        <v>20.9</v>
+        <v>19.5</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>16.6</v>
       </c>
       <c r="F3">
-        <v>8.300000000000001</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
       <c r="H3">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="I3">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J3">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="K3">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>94.2</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1738,189 +1776,189 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="C4">
-        <v>24.4</v>
+        <v>20.7</v>
       </c>
       <c r="D4">
-        <v>17.1</v>
+        <v>19.8</v>
       </c>
       <c r="E4">
-        <v>12.6</v>
+        <v>15.5</v>
       </c>
       <c r="F4">
-        <v>9.1</v>
+        <v>14.9</v>
       </c>
       <c r="G4">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="H4">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>93.59999999999999</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B5">
-        <v>5.9</v>
+        <v>13.8</v>
       </c>
       <c r="C5">
-        <v>10.5</v>
+        <v>19.3</v>
       </c>
       <c r="D5">
-        <v>14.2</v>
+        <v>20.2</v>
       </c>
       <c r="E5">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="F5">
-        <v>15.3</v>
+        <v>14.4</v>
       </c>
       <c r="G5">
-        <v>14.7</v>
+        <v>7.3</v>
       </c>
       <c r="H5">
-        <v>9.699999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="I5">
-        <v>7.7</v>
+        <v>1.6</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>0.3</v>
       </c>
       <c r="K5">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>76.09999999999999</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B6">
-        <v>2.7</v>
+        <v>7.8</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>11.8</v>
       </c>
       <c r="D6">
-        <v>9.1</v>
+        <v>15.9</v>
       </c>
       <c r="E6">
-        <v>16.5</v>
+        <v>19.1</v>
       </c>
       <c r="F6">
-        <v>14.5</v>
+        <v>21.9</v>
       </c>
       <c r="G6">
-        <v>16.4</v>
+        <v>13.2</v>
       </c>
       <c r="H6">
-        <v>14.5</v>
+        <v>7</v>
       </c>
       <c r="I6">
-        <v>10.2</v>
+        <v>2.4</v>
       </c>
       <c r="J6">
-        <v>6.8</v>
+        <v>0.8</v>
       </c>
       <c r="K6">
-        <v>3.3</v>
+        <v>0.1</v>
       </c>
       <c r="L6">
-        <v>65.2</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="C7">
+        <v>2.4</v>
+      </c>
+      <c r="D7">
         <v>5.6</v>
       </c>
-      <c r="D7">
-        <v>9.6</v>
-      </c>
       <c r="E7">
-        <v>14.1</v>
+        <v>11</v>
       </c>
       <c r="F7">
-        <v>16.8</v>
+        <v>15.8</v>
       </c>
       <c r="G7">
-        <v>14.5</v>
+        <v>25.2</v>
       </c>
       <c r="H7">
-        <v>13.1</v>
+        <v>19.2</v>
       </c>
       <c r="I7">
         <v>11.6</v>
       </c>
       <c r="J7">
-        <v>9.1</v>
+        <v>5.6</v>
       </c>
       <c r="K7">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="L7">
-        <v>62.6</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B8">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="C8">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="D8">
-        <v>7.3</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>10.6</v>
+        <v>4</v>
       </c>
       <c r="F8">
-        <v>13.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G8">
-        <v>15.8</v>
+        <v>18.7</v>
       </c>
       <c r="H8">
-        <v>15.2</v>
+        <v>28</v>
       </c>
       <c r="I8">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="J8">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="K8">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="L8">
-        <v>53.5</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1928,37 +1966,37 @@
         <v>0</v>
       </c>
       <c r="B9">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="D9">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="E9">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="F9">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="G9">
-        <v>9.4</v>
+        <v>11.1</v>
       </c>
       <c r="H9">
-        <v>14.5</v>
+        <v>17.6</v>
       </c>
       <c r="I9">
-        <v>16.2</v>
+        <v>27.4</v>
       </c>
       <c r="J9">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="K9">
-        <v>25.6</v>
+        <v>14.6</v>
       </c>
       <c r="L9">
-        <v>21.2</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1969,34 +2007,34 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="F10">
-        <v>5.6</v>
+        <v>1.7</v>
       </c>
       <c r="G10">
-        <v>8.6</v>
+        <v>5.1</v>
       </c>
       <c r="H10">
-        <v>12.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I10">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="J10">
-        <v>20.3</v>
+        <v>30.3</v>
       </c>
       <c r="K10">
-        <v>31.3</v>
+        <v>34.7</v>
       </c>
       <c r="L10">
-        <v>18.7</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2004,37 +2042,37 @@
         <v>4</v>
       </c>
       <c r="B11">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>2.3</v>
+        <v>0.2</v>
       </c>
       <c r="F11">
-        <v>6.5</v>
+        <v>0.9</v>
       </c>
       <c r="G11">
-        <v>7.4</v>
+        <v>3.4</v>
       </c>
       <c r="H11">
-        <v>12.2</v>
+        <v>8.5</v>
       </c>
       <c r="I11">
-        <v>18.7</v>
+        <v>17.1</v>
       </c>
       <c r="J11">
-        <v>23.7</v>
+        <v>28.1</v>
       </c>
       <c r="K11">
-        <v>27.2</v>
+        <v>41.8</v>
       </c>
       <c r="L11">
-        <v>18.2</v>
+        <v>4.5</v>
       </c>
     </row>
   </sheetData>
@@ -2044,58 +2082,67 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>35</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2">
+        <v>69.39999999999999</v>
+      </c>
+      <c r="C2">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="D2">
+        <v>94.39999999999999</v>
+      </c>
+      <c r="E2">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="F2">
+        <v>99.2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2">
+      <c r="B3">
         <v>100</v>
       </c>
-      <c r="C2">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="D2">
+      <c r="C3">
+        <v>99.8</v>
+      </c>
+      <c r="D3">
         <v>97.39999999999999</v>
       </c>
-      <c r="E2">
-        <v>97.3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3">
-        <v>73.5</v>
-      </c>
-      <c r="C3">
-        <v>96.2</v>
-      </c>
-      <c r="D3">
-        <v>95.09999999999999</v>
-      </c>
       <c r="E3">
-        <v>94.59999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>97.2</v>
+      </c>
+      <c r="F3">
+        <v>96.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -2103,132 +2150,156 @@
         <v>99.90000000000001</v>
       </c>
       <c r="C4">
-        <v>50</v>
+        <v>51.4</v>
       </c>
       <c r="D4">
+        <v>93.7</v>
+      </c>
+      <c r="E4">
+        <v>96.7</v>
+      </c>
+      <c r="F4">
+        <v>95.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
+        <v>8.1</v>
+      </c>
+      <c r="C5">
+        <v>42.7</v>
+      </c>
+      <c r="D5">
+        <v>51.2</v>
+      </c>
+      <c r="E5">
+        <v>95.89999999999999</v>
+      </c>
+      <c r="F5">
+        <v>94.59999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>81.3</v>
+      </c>
+      <c r="C6">
+        <v>89</v>
+      </c>
+      <c r="D6">
+        <v>62.2</v>
+      </c>
+      <c r="E6">
+        <v>91.60000000000001</v>
+      </c>
+      <c r="F6">
+        <v>90.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>100</v>
+      </c>
+      <c r="C7">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="D7">
+        <v>69.69999999999999</v>
+      </c>
+      <c r="E7">
+        <v>61</v>
+      </c>
+      <c r="F7">
+        <v>56.99999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>40.6</v>
+      </c>
+      <c r="C8">
         <v>95.5</v>
       </c>
-      <c r="E4">
-        <v>92.60000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5">
-        <v>37.1</v>
-      </c>
-      <c r="C5">
-        <v>95.5</v>
-      </c>
-      <c r="D5">
-        <v>78.8</v>
-      </c>
-      <c r="E5">
-        <v>73.8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>100</v>
-      </c>
-      <c r="C6">
-        <v>96.8</v>
-      </c>
-      <c r="D6">
-        <v>68.8</v>
-      </c>
-      <c r="E6">
-        <v>66.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7">
-        <v>80.2</v>
-      </c>
-      <c r="C7">
-        <v>90.7</v>
-      </c>
-      <c r="D7">
-        <v>63.5</v>
-      </c>
-      <c r="E7">
-        <v>65.60000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>8.200000000000001</v>
-      </c>
-      <c r="C8">
-        <v>40.7</v>
-      </c>
       <c r="D8">
-        <v>53.40000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="E8">
-        <v>53.90000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>30.7</v>
+      </c>
+      <c r="F8">
+        <v>33.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B9">
-        <v>88.2</v>
+        <v>89.2</v>
       </c>
       <c r="C9">
-        <v>16.4</v>
+        <v>18.1</v>
       </c>
       <c r="D9">
-        <v>17.7</v>
+        <v>21</v>
       </c>
       <c r="E9">
-        <v>22.7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>17.4</v>
+      </c>
+      <c r="F9">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10">
+        <v>0.2</v>
+      </c>
+      <c r="C10">
+        <v>7.7</v>
+      </c>
+      <c r="D10">
+        <v>18.8</v>
+      </c>
+      <c r="E10">
+        <v>6</v>
+      </c>
+      <c r="F10">
+        <v>8.799999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10">
-        <v>12.7</v>
-      </c>
-      <c r="C10">
-        <v>4.6</v>
-      </c>
-      <c r="D10">
-        <v>13.7</v>
-      </c>
-      <c r="E10">
-        <v>17.7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="B11">
-        <v>0.2</v>
+        <v>11.3</v>
       </c>
       <c r="C11">
-        <v>9.199999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="D11">
-        <v>16.1</v>
+        <v>13.9</v>
       </c>
       <c r="E11">
-        <v>15.3</v>
+        <v>4.100000000000001</v>
+      </c>
+      <c r="F11">
+        <v>5.600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2243,28 +2314,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2272,28 +2343,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D2">
-        <v>100.86</v>
+        <v>112.13</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>116.33</v>
+        <v>115.35</v>
       </c>
       <c r="G2">
-        <v>0.485</v>
+        <v>0.5</v>
       </c>
       <c r="H2">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2301,28 +2372,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D3">
-        <v>121</v>
+        <v>101.94</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>115.42</v>
+        <v>116.28</v>
       </c>
       <c r="G3">
-        <v>0.485</v>
+        <v>0.475</v>
       </c>
       <c r="H3">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="I3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2330,28 +2401,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D4">
-        <v>117</v>
+        <v>124.35</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>114.56</v>
+        <v>117.17</v>
       </c>
       <c r="G4">
-        <v>0.515</v>
+        <v>0.45</v>
       </c>
       <c r="H4">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2359,28 +2430,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D5">
-        <v>119.33</v>
+        <v>119.81</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>115.72</v>
+        <v>116.75</v>
       </c>
       <c r="G5">
-        <v>0.424</v>
+        <v>0.55</v>
       </c>
       <c r="H5">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="I5">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2388,28 +2459,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D6">
-        <v>116.77</v>
+        <v>125.26</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>115.98</v>
+        <v>116.41</v>
       </c>
       <c r="G6">
-        <v>0.515</v>
+        <v>0.475</v>
       </c>
       <c r="H6">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2417,28 +2488,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D7">
-        <v>103.31</v>
+        <v>124.9</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>116.19</v>
+        <v>116.48</v>
       </c>
       <c r="G7">
-        <v>0.515</v>
+        <v>0.525</v>
       </c>
       <c r="H7">
-        <v>-0.6</v>
+        <v>-0.2</v>
       </c>
       <c r="I7">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2449,25 +2520,25 @@
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D8">
-        <v>108.81</v>
+        <v>122.9</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F8">
-        <v>114.83</v>
+        <v>116.13</v>
       </c>
       <c r="G8">
-        <v>0.455</v>
+        <v>0.45</v>
       </c>
       <c r="H8">
-        <v>-0.6</v>
+        <v>-0.8</v>
       </c>
       <c r="I8">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2478,25 +2549,25 @@
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D9">
-        <v>104.87</v>
+        <v>100.34</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
       </c>
       <c r="F9">
-        <v>115.18</v>
+        <v>116.6</v>
       </c>
       <c r="G9">
-        <v>0.576</v>
+        <v>0.525</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>-0.9</v>
       </c>
       <c r="I9">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2504,28 +2575,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D10">
-        <v>123.97</v>
+        <v>131.65</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
       </c>
       <c r="F10">
-        <v>113.21</v>
+        <v>115.71</v>
       </c>
       <c r="G10">
-        <v>0.485</v>
+        <v>0.55</v>
       </c>
       <c r="H10">
-        <v>-1.4</v>
+        <v>-0.9</v>
       </c>
       <c r="I10">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2533,28 +2604,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D11">
-        <v>135.7</v>
+        <v>101.16</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
       </c>
       <c r="F11">
-        <v>114.21</v>
+        <v>117.54</v>
       </c>
       <c r="G11">
-        <v>0.545</v>
+        <v>0.5</v>
       </c>
       <c r="H11">
-        <v>-1.5</v>
+        <v>-1.4</v>
       </c>
       <c r="I11">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2569,89 +2640,89 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C2">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>135.7</v>
+        <v>124.355</v>
       </c>
       <c r="E2">
-        <v>407.1</v>
+        <v>497.42</v>
       </c>
       <c r="F2">
-        <v>96.7</v>
+        <v>98.7</v>
       </c>
       <c r="G2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D3">
-        <v>119.3333333333333</v>
+        <v>131.645</v>
       </c>
       <c r="E3">
-        <v>358</v>
+        <v>526.58</v>
       </c>
       <c r="F3">
-        <v>94.19999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="G3">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2659,144 +2730,144 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C4">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="D4">
-        <v>123.9666666666667</v>
+        <v>125.26</v>
       </c>
       <c r="E4">
-        <v>371.9</v>
+        <v>501.04</v>
       </c>
       <c r="F4">
-        <v>93.60000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="G4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C5">
-        <v>0.3333333333333333</v>
+        <v>0.75</v>
       </c>
       <c r="D5">
-        <v>121</v>
+        <v>122.9</v>
       </c>
       <c r="E5">
-        <v>363</v>
+        <v>491.6</v>
       </c>
       <c r="F5">
-        <v>76.09999999999999</v>
+        <v>94</v>
       </c>
       <c r="G5">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C6">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="D6">
-        <v>117</v>
+        <v>124.9</v>
       </c>
       <c r="E6">
-        <v>351</v>
+        <v>499.6</v>
       </c>
       <c r="F6">
-        <v>65.2</v>
+        <v>89.7</v>
       </c>
       <c r="G6">
-        <v>3.3</v>
+        <v>0.1</v>
       </c>
       <c r="H6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C7">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="D7">
-        <v>116.7666666666667</v>
+        <v>119.805</v>
       </c>
       <c r="E7">
-        <v>350.3</v>
+        <v>479.22</v>
       </c>
       <c r="F7">
-        <v>62.6</v>
+        <v>60.9</v>
       </c>
       <c r="G7">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="H7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C8">
-        <v>0.6666666666666666</v>
+        <v>0.25</v>
       </c>
       <c r="D8">
-        <v>108.8133333333333</v>
+        <v>112.13</v>
       </c>
       <c r="E8">
-        <v>326.44</v>
+        <v>448.52</v>
       </c>
       <c r="F8">
-        <v>53.5</v>
+        <v>34.2</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="H8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2804,28 +2875,28 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C9">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="D9">
-        <v>100.86</v>
+        <v>101.94</v>
       </c>
       <c r="E9">
-        <v>302.58</v>
+        <v>407.76</v>
       </c>
       <c r="F9">
-        <v>21.2</v>
+        <v>17.4</v>
       </c>
       <c r="G9">
-        <v>25.6</v>
+        <v>14.6</v>
       </c>
       <c r="H9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2833,28 +2904,28 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C10">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="D10">
-        <v>103.3133333333333</v>
+        <v>101.16</v>
       </c>
       <c r="E10">
-        <v>309.94</v>
+        <v>404.64</v>
       </c>
       <c r="F10">
-        <v>18.7</v>
+        <v>7.199999999999999</v>
       </c>
       <c r="G10">
-        <v>31.3</v>
+        <v>34.7</v>
       </c>
       <c r="H10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2862,28 +2933,28 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C11">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="D11">
-        <v>104.8733333333333</v>
+        <v>100.335</v>
       </c>
       <c r="E11">
-        <v>314.62</v>
+        <v>401.34</v>
       </c>
       <c r="F11">
-        <v>18.2</v>
+        <v>4.5</v>
       </c>
       <c r="G11">
-        <v>27.2</v>
+        <v>41.8</v>
       </c>
       <c r="H11" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I11" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -2898,19 +2969,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2918,19 +2989,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D2">
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2941,16 +3012,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2958,19 +3029,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2981,16 +3052,16 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2998,19 +3069,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3018,19 +3089,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D7">
         <v>-1</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3038,19 +3109,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3058,19 +3129,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D9">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3078,19 +3149,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C10" t="s">
         <v>44</v>
       </c>
       <c r="D10">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3101,16 +3172,16 @@
         <v>0</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D11">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -3120,41 +3191,47 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>96</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D2">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>6</v>
+      </c>
+      <c r="E2">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -3167,28 +3244,34 @@
       <c r="D3">
         <v>10</v>
       </c>
-      <c r="E3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="E3">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D4">
-        <v>6</v>
-      </c>
-      <c r="E4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>12</v>
+      </c>
+      <c r="E4">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -3201,96 +3284,114 @@
       <c r="D5">
         <v>1</v>
       </c>
-      <c r="E5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6">
+        <v>-2</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>-2</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6">
+      <c r="B7">
         <v>-5</v>
       </c>
-      <c r="C6">
+      <c r="C7">
         <v>-4</v>
-      </c>
-      <c r="D6">
-        <v>-1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7">
-        <v>-4</v>
-      </c>
-      <c r="C7">
-        <v>-6</v>
       </c>
       <c r="D7">
         <v>-1</v>
       </c>
-      <c r="E7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="E7">
+        <v>-1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="C8">
+        <v>-6</v>
+      </c>
+      <c r="D8">
+        <v>-1</v>
+      </c>
+      <c r="E8">
+        <v>-4</v>
+      </c>
+      <c r="F8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9">
         <v>1</v>
       </c>
-      <c r="D8">
-        <v>-2</v>
-      </c>
-      <c r="E8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="1" t="s">
+      <c r="D9">
+        <v>-10</v>
+      </c>
+      <c r="E9">
+        <v>-6</v>
+      </c>
+      <c r="F9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B9">
+      <c r="B10">
         <v>1</v>
       </c>
-      <c r="C9">
+      <c r="C10">
         <v>2</v>
       </c>
-      <c r="D9">
+      <c r="D10">
         <v>-4</v>
       </c>
-      <c r="E9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10">
-        <v>4</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>-10</v>
-      </c>
-      <c r="E10" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="E10">
+        <v>-11</v>
+      </c>
+      <c r="F10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
@@ -3303,8 +3404,11 @@
       <c r="D11">
         <v>-11</v>
       </c>
-      <c r="E11" t="s">
-        <v>89</v>
+      <c r="E11">
+        <v>-12</v>
+      </c>
+      <c r="F11" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Brown Munde 2026.xlsx
+++ b/data/leagues/Brown Munde 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="108">
   <si>
     <t>Still Rollin'</t>
   </si>
@@ -55,19 +55,19 @@
     <t>BurgerBoyz</t>
   </si>
   <si>
-    <t>2-2-0</t>
-  </si>
-  <si>
-    <t>3-1-0</t>
-  </si>
-  <si>
-    <t>1-3-0</t>
-  </si>
-  <si>
-    <t>4-0-0</t>
-  </si>
-  <si>
-    <t>0-4-0</t>
+    <t>3-2-0</t>
+  </si>
+  <si>
+    <t>4-1-0</t>
+  </si>
+  <si>
+    <t>2-3-0</t>
+  </si>
+  <si>
+    <t>5-0-0</t>
+  </si>
+  <si>
+    <t>1-4-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -136,6 +136,9 @@
     <t>Week_5</t>
   </si>
   <si>
+    <t>Week_6</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -157,36 +160,36 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Prahlad Singh</t>
+  </si>
+  <si>
+    <t>Kiran MADUGULA</t>
+  </si>
+  <si>
     <t>KASHYAP AShok</t>
   </si>
   <si>
-    <t>Prahlad Singh</t>
+    <t>suraj bhalani</t>
   </si>
   <si>
     <t>Utkarsh Gupta</t>
   </si>
   <si>
+    <t>Guruansh Singh</t>
+  </si>
+  <si>
+    <t>Harshit Aggarwal</t>
+  </si>
+  <si>
+    <t>Pawan Bhambhwani</t>
+  </si>
+  <si>
     <t>Krishna Padodara</t>
   </si>
   <si>
-    <t>Pawan Bhambhwani</t>
-  </si>
-  <si>
-    <t>Harshit Aggarwal</t>
-  </si>
-  <si>
-    <t>Kiran MADUGULA</t>
-  </si>
-  <si>
     <t>Hark Nanda</t>
   </si>
   <si>
-    <t>Guruansh Singh</t>
-  </si>
-  <si>
-    <t>suraj bhalani</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -211,46 +214,52 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>4-0</t>
-  </si>
-  <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>3-1</t>
-  </si>
-  <si>
-    <t>1-3</t>
-  </si>
-  <si>
-    <t>9.8-4.1-0.1</t>
-  </si>
-  <si>
-    <t>8.7-5.2-0.1</t>
-  </si>
-  <si>
-    <t>8.9-5.0-0.1</t>
-  </si>
-  <si>
-    <t>7.9-5.9-0.1</t>
-  </si>
-  <si>
-    <t>6.4-7.5-0.1</t>
-  </si>
-  <si>
-    <t>5.7-8.2-0.1</t>
-  </si>
-  <si>
-    <t>5.2-8.7-0.1</t>
+    <t>5-0</t>
+  </si>
+  <si>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>10.9-3.0-0.1</t>
+  </si>
+  <si>
+    <t>9.2-4.7-0.1</t>
+  </si>
+  <si>
+    <t>7.7-6.2-0.1</t>
+  </si>
+  <si>
+    <t>7.4-6.5-0.1</t>
+  </si>
+  <si>
+    <t>7.0-6.9-0.1</t>
+  </si>
+  <si>
+    <t>6.8-7.1-0.1</t>
+  </si>
+  <si>
+    <t>6.3-7.6-0.1</t>
+  </si>
+  <si>
+    <t>5.3-8.6-0.1</t>
+  </si>
+  <si>
+    <t>4.8-9.1-0.1</t>
   </si>
   <si>
     <t>4.2-9.7-0.1</t>
   </si>
   <si>
-    <t>4.0-9.9-0.1</t>
-  </si>
-  <si>
-    <t>10-4</t>
+    <t>11-3</t>
   </si>
   <si>
     <t>9-5</t>
@@ -259,6 +268,9 @@
     <t>8-6</t>
   </si>
   <si>
+    <t>7-7</t>
+  </si>
+  <si>
     <t>6-8</t>
   </si>
   <si>
@@ -277,33 +289,30 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↑6</t>
+    <t>↓1</t>
+  </si>
+  <si>
+    <t>↓4</t>
+  </si>
+  <si>
+    <t>↑8</t>
+  </si>
+  <si>
+    <t>↑10</t>
+  </si>
+  <si>
+    <t>↓2</t>
   </si>
   <si>
     <t>↑1</t>
   </si>
   <si>
+    <t>↓3</t>
+  </si>
+  <si>
     <t>↓5</t>
   </si>
   <si>
-    <t>↑3</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>↓3</t>
-  </si>
-  <si>
-    <t>↑4</t>
-  </si>
-  <si>
-    <t>↓7</t>
-  </si>
-  <si>
-    <t>↓1</t>
-  </si>
-  <si>
     <t>Week 1</t>
   </si>
   <si>
@@ -314,6 +323,9 @@
   </si>
   <si>
     <t>Week 4</t>
+  </si>
+  <si>
+    <t>Week 5</t>
   </si>
   <si>
     <t>Week</t>
@@ -735,7 +747,7 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -744,19 +756,19 @@
         <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I2" t="s">
         <v>12</v>
       </c>
       <c r="J2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K2" t="s">
         <v>10</v>
@@ -767,34 +779,34 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -805,7 +817,7 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -814,19 +826,19 @@
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
         <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K4" t="s">
         <v>11</v>
@@ -840,28 +852,28 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5" t="s">
         <v>10</v>
       </c>
       <c r="H5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K5" t="s">
         <v>11</v>
@@ -884,19 +896,19 @@
         <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G6" t="s">
         <v>12</v>
       </c>
       <c r="H6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I6" t="s">
         <v>12</v>
       </c>
       <c r="J6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K6" t="s">
         <v>11</v>
@@ -919,19 +931,19 @@
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
         <v>12</v>
       </c>
       <c r="H7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I7" t="s">
         <v>10</v>
       </c>
       <c r="J7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K7" t="s">
         <v>11</v>
@@ -977,31 +989,31 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>10</v>
       </c>
       <c r="H9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K9" t="s">
         <v>11</v>
@@ -1012,34 +1024,34 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G10" t="s">
         <v>10</v>
       </c>
       <c r="H10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I10" t="s">
+        <v>10</v>
+      </c>
+      <c r="J10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K10" t="s">
         <v>11</v>
-      </c>
-      <c r="J10" t="s">
-        <v>10</v>
-      </c>
-      <c r="K10" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1059,7 +1071,7 @@
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G11" t="s">
         <v>10</v>
@@ -1084,30 +1096,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1141,25 +1153,25 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>-2</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>-13</v>
       </c>
       <c r="G3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1170,22 +1182,22 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4">
-        <v>-7</v>
+        <v>10</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1193,25 +1205,25 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>-7</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1219,22 +1231,22 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" t="s">
         <v>9</v>
       </c>
-      <c r="D6" t="s">
-        <v>0</v>
-      </c>
       <c r="E6">
-        <v>-4</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H6" t="s">
         <v>9</v>
@@ -1245,25 +1257,25 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7">
         <v>0</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7">
         <v>6</v>
       </c>
-      <c r="E7">
-        <v>-11</v>
-      </c>
-      <c r="F7">
-        <v>-10</v>
-      </c>
       <c r="G7">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H7" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1271,25 +1283,77 @@
         <v>6</v>
       </c>
       <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>-4</v>
+      </c>
+      <c r="F8">
+        <v>-2</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9">
         <v>4</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C9" t="s">
         <v>5</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D9" t="s">
         <v>7</v>
       </c>
-      <c r="E8">
+      <c r="E9">
         <v>2</v>
       </c>
-      <c r="F8">
+      <c r="F9">
         <v>1</v>
       </c>
-      <c r="G8">
+      <c r="G9">
         <v>1</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H9" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10">
+        <v>-11</v>
+      </c>
+      <c r="F10">
+        <v>-10</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" t="s">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1318,13 +1382,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1332,10 +1396,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
@@ -1346,13 +1410,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1360,13 +1424,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1374,13 +1438,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1388,10 +1452,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
@@ -1402,10 +1466,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -1416,13 +1480,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1430,13 +1494,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1447,7 +1511,7 @@
         <v>9</v>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="D11" t="s">
         <v>13</v>
@@ -1485,10 +1549,10 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="D2">
-        <v>-1.1</v>
+        <v>-1.2</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
@@ -1502,10 +1566,10 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -1519,13 +1583,13 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="D4">
-        <v>0.5</v>
+        <v>0.7999999999999998</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1533,16 +1597,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C5">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D5">
-        <v>0.3999999999999999</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1553,13 +1617,13 @@
         <v>7</v>
       </c>
       <c r="C6">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="D6">
-        <v>-0.7000000000000002</v>
+        <v>-0.5</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1567,13 +1631,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C7">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="D7">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
@@ -1584,13 +1648,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="D8">
-        <v>0.6000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="E8" t="s">
         <v>12</v>
@@ -1601,16 +1665,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="D9">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1618,16 +1682,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="D10">
-        <v>0.3999999999999999</v>
+        <v>-1.2</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1635,16 +1699,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="D11">
-        <v>-0.8</v>
+        <v>0.5</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1700,28 +1764,28 @@
         <v>9</v>
       </c>
       <c r="B2">
-        <v>36.5</v>
+        <v>72.7</v>
       </c>
       <c r="C2">
-        <v>24.2</v>
+        <v>17.1</v>
       </c>
       <c r="D2">
-        <v>16.5</v>
+        <v>7.4</v>
       </c>
       <c r="E2">
-        <v>12.5</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>6.3</v>
+        <v>0.6</v>
       </c>
       <c r="G2">
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="I2">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1730,83 +1794,83 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>98.7</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>21.9</v>
+        <v>16.7</v>
       </c>
       <c r="C3">
-        <v>20.7</v>
+        <v>35.6</v>
       </c>
       <c r="D3">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>16.6</v>
+        <v>12.9</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>6.1</v>
       </c>
       <c r="G3">
-        <v>6.5</v>
+        <v>3.8</v>
       </c>
       <c r="H3">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="I3">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
         <v>0.2</v>
       </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
       <c r="L3">
-        <v>97.2</v>
+        <v>98.09999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B4">
-        <v>18.5</v>
+        <v>6.3</v>
       </c>
       <c r="C4">
-        <v>20.7</v>
+        <v>19</v>
       </c>
       <c r="D4">
-        <v>19.8</v>
+        <v>22.3</v>
       </c>
       <c r="E4">
-        <v>15.5</v>
+        <v>20.3</v>
       </c>
       <c r="F4">
-        <v>14.9</v>
+        <v>13.1</v>
       </c>
       <c r="G4">
-        <v>6.8</v>
+        <v>8.9</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>5.7</v>
       </c>
       <c r="I4">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L4">
-        <v>96.2</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1814,37 +1878,37 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>13.8</v>
+        <v>2.1</v>
       </c>
       <c r="C5">
-        <v>19.3</v>
+        <v>12.7</v>
       </c>
       <c r="D5">
-        <v>20.2</v>
+        <v>13.7</v>
       </c>
       <c r="E5">
-        <v>19</v>
+        <v>16.6</v>
       </c>
       <c r="F5">
-        <v>14.4</v>
+        <v>18.3</v>
       </c>
       <c r="G5">
-        <v>7.3</v>
+        <v>15.6</v>
       </c>
       <c r="H5">
-        <v>4.1</v>
+        <v>9.9</v>
       </c>
       <c r="I5">
-        <v>1.6</v>
+        <v>6.8</v>
       </c>
       <c r="J5">
-        <v>0.3</v>
+        <v>3.3</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>94</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1852,156 +1916,156 @@
         <v>3</v>
       </c>
       <c r="B6">
-        <v>7.8</v>
+        <v>1.5</v>
       </c>
       <c r="C6">
-        <v>11.8</v>
+        <v>7.4</v>
       </c>
       <c r="D6">
-        <v>15.9</v>
+        <v>13.4</v>
       </c>
       <c r="E6">
-        <v>19.1</v>
+        <v>16.7</v>
       </c>
       <c r="F6">
-        <v>21.9</v>
+        <v>20.4</v>
       </c>
       <c r="G6">
-        <v>13.2</v>
+        <v>15.6</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>12.6</v>
       </c>
       <c r="I6">
-        <v>2.4</v>
+        <v>7.9</v>
       </c>
       <c r="J6">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="K6">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="L6">
-        <v>89.7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>0.5</v>
+      </c>
+      <c r="C7">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>0.9</v>
-      </c>
-      <c r="C7">
-        <v>2.4</v>
-      </c>
       <c r="D7">
-        <v>5.6</v>
+        <v>12.8</v>
       </c>
       <c r="E7">
-        <v>11</v>
+        <v>16.3</v>
       </c>
       <c r="F7">
-        <v>15.8</v>
+        <v>18.3</v>
       </c>
       <c r="G7">
-        <v>25.2</v>
+        <v>16.9</v>
       </c>
       <c r="H7">
-        <v>19.2</v>
+        <v>14.8</v>
       </c>
       <c r="I7">
-        <v>11.6</v>
+        <v>7.8</v>
       </c>
       <c r="J7">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="K7">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="L7">
-        <v>60.9</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B8">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F8">
-        <v>8.199999999999999</v>
+        <v>11.3</v>
       </c>
       <c r="G8">
-        <v>18.7</v>
+        <v>17.3</v>
       </c>
       <c r="H8">
-        <v>28</v>
+        <v>18.5</v>
       </c>
       <c r="I8">
-        <v>20</v>
+        <v>17.8</v>
       </c>
       <c r="J8">
-        <v>11.7</v>
+        <v>13.4</v>
       </c>
       <c r="K8">
-        <v>6.1</v>
+        <v>7.3</v>
       </c>
       <c r="L8">
-        <v>34.2</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C9">
         <v>0.2</v>
       </c>
       <c r="D9">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="E9">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="F9">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
       <c r="G9">
-        <v>11.1</v>
+        <v>8.9</v>
       </c>
       <c r="H9">
-        <v>17.6</v>
+        <v>14.9</v>
       </c>
       <c r="I9">
-        <v>27.4</v>
+        <v>22.5</v>
       </c>
       <c r="J9">
-        <v>23</v>
+        <v>24.4</v>
       </c>
       <c r="K9">
-        <v>14.6</v>
+        <v>18.7</v>
       </c>
       <c r="L9">
-        <v>17.4</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2010,69 +2074,69 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="E10">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="F10">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="G10">
-        <v>5.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H10">
-        <v>9.800000000000001</v>
+        <v>14.3</v>
       </c>
       <c r="I10">
-        <v>18</v>
+        <v>19.8</v>
       </c>
       <c r="J10">
-        <v>30.3</v>
+        <v>25.1</v>
       </c>
       <c r="K10">
-        <v>34.7</v>
+        <v>24.1</v>
       </c>
       <c r="L10">
-        <v>7.2</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E11">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="F11">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="G11">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="H11">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="I11">
-        <v>17.1</v>
+        <v>14.6</v>
       </c>
       <c r="J11">
-        <v>28.1</v>
+        <v>24.4</v>
       </c>
       <c r="K11">
-        <v>41.8</v>
+        <v>45.2</v>
       </c>
       <c r="L11">
-        <v>4.5</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -2082,10 +2146,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
         <v>32</v>
       </c>
@@ -2101,205 +2165,238 @@
       <c r="F1" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B2">
+        <v>72.39999999999999</v>
+      </c>
+      <c r="C2">
+        <v>94.5</v>
+      </c>
+      <c r="D2">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="E2">
+        <v>99.3</v>
+      </c>
+      <c r="F2">
+        <v>99.7</v>
+      </c>
+      <c r="G2">
+        <v>99.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="C3">
+        <v>50.8</v>
+      </c>
+      <c r="D3">
+        <v>94.5</v>
+      </c>
+      <c r="E3">
+        <v>97</v>
+      </c>
+      <c r="F3">
+        <v>95.7</v>
+      </c>
+      <c r="G3">
+        <v>96.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>100</v>
+      </c>
+      <c r="C4">
+        <v>97.8</v>
+      </c>
+      <c r="D4">
         <v>69.39999999999999</v>
       </c>
-      <c r="C2">
-        <v>95.09999999999999</v>
-      </c>
-      <c r="D2">
-        <v>94.39999999999999</v>
-      </c>
-      <c r="E2">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="F2">
-        <v>99.2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3">
-        <v>100</v>
-      </c>
-      <c r="C3">
-        <v>99.8</v>
-      </c>
-      <c r="D3">
-        <v>97.39999999999999</v>
-      </c>
-      <c r="E3">
-        <v>97.2</v>
-      </c>
-      <c r="F3">
-        <v>96.3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="C4">
-        <v>51.4</v>
-      </c>
-      <c r="D4">
-        <v>93.7</v>
-      </c>
       <c r="E4">
-        <v>96.7</v>
+        <v>63.5</v>
       </c>
       <c r="F4">
-        <v>95.8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>91.8</v>
+      </c>
+      <c r="G4">
+        <v>89.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B5">
-        <v>8.1</v>
+        <v>8.799999999999999</v>
       </c>
       <c r="C5">
-        <v>42.7</v>
+        <v>43</v>
       </c>
       <c r="D5">
-        <v>51.2</v>
+        <v>54</v>
       </c>
       <c r="E5">
-        <v>95.89999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="F5">
-        <v>94.59999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>81.2</v>
+      </c>
+      <c r="G5">
+        <v>79.90000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B6">
-        <v>81.3</v>
+        <v>79.60000000000001</v>
       </c>
       <c r="C6">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D6">
-        <v>62.2</v>
+        <v>58.2</v>
       </c>
       <c r="E6">
-        <v>91.60000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="F6">
-        <v>90.8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>75.3</v>
+      </c>
+      <c r="G6">
+        <v>77.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>100</v>
       </c>
       <c r="C7">
-        <v>97.59999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D7">
-        <v>69.69999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="E7">
-        <v>61</v>
+        <v>96.8</v>
       </c>
       <c r="F7">
-        <v>56.99999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>69.5</v>
+      </c>
+      <c r="G7">
+        <v>72.39999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="C8">
+        <v>19.6</v>
+      </c>
+      <c r="D8">
+        <v>20.8</v>
+      </c>
+      <c r="E8">
+        <v>16.6</v>
+      </c>
+      <c r="F8">
+        <v>39.7</v>
+      </c>
+      <c r="G8">
+        <v>41.09999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9">
+        <v>0.2</v>
+      </c>
+      <c r="C9">
+        <v>7.5</v>
+      </c>
+      <c r="D9">
+        <v>12</v>
+      </c>
+      <c r="E9">
+        <v>6.600000000000001</v>
+      </c>
+      <c r="F9">
+        <v>22.6</v>
+      </c>
+      <c r="G9">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10">
+        <v>12.1</v>
+      </c>
+      <c r="C10">
+        <v>3.5</v>
+      </c>
+      <c r="D10">
+        <v>17.8</v>
+      </c>
+      <c r="E10">
+        <v>4.100000000000001</v>
+      </c>
+      <c r="F10">
+        <v>15.3</v>
+      </c>
+      <c r="G10">
+        <v>16.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B8">
-        <v>40.6</v>
-      </c>
-      <c r="C8">
-        <v>95.5</v>
-      </c>
-      <c r="D8">
-        <v>77.7</v>
-      </c>
-      <c r="E8">
-        <v>30.7</v>
-      </c>
-      <c r="F8">
-        <v>33.6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9">
-        <v>89.2</v>
-      </c>
-      <c r="C9">
-        <v>18.1</v>
-      </c>
-      <c r="D9">
-        <v>21</v>
-      </c>
-      <c r="E9">
-        <v>17.4</v>
-      </c>
-      <c r="F9">
-        <v>18.3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10">
-        <v>0.2</v>
-      </c>
-      <c r="C10">
-        <v>7.7</v>
-      </c>
-      <c r="D10">
-        <v>18.8</v>
-      </c>
-      <c r="E10">
-        <v>6</v>
-      </c>
-      <c r="F10">
-        <v>8.799999999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="B11">
-        <v>11.3</v>
+        <v>36.6</v>
       </c>
       <c r="C11">
-        <v>3.1</v>
+        <v>95.39999999999999</v>
       </c>
       <c r="D11">
-        <v>13.9</v>
+        <v>79.5</v>
       </c>
       <c r="E11">
-        <v>4.100000000000001</v>
+        <v>32.5</v>
       </c>
       <c r="F11">
-        <v>5.600000000000001</v>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G11">
+        <v>5.800000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2317,25 +2414,25 @@
         <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2343,28 +2440,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2">
-        <v>112.13</v>
+        <v>107.92</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>115.35</v>
+        <v>119.58</v>
       </c>
       <c r="G2">
-        <v>0.5</v>
+        <v>0.444</v>
       </c>
       <c r="H2">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2372,28 +2469,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D3">
-        <v>101.94</v>
+        <v>120.55</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3">
-        <v>116.28</v>
+        <v>122.19</v>
       </c>
       <c r="G3">
-        <v>0.475</v>
+        <v>0.467</v>
       </c>
       <c r="H3">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="I3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2401,28 +2498,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4">
+        <v>106.9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4">
+        <v>120.77</v>
+      </c>
+      <c r="G4">
+        <v>0.533</v>
+      </c>
+      <c r="H4">
+        <v>1.9</v>
+      </c>
+      <c r="I4">
         <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4">
-        <v>124.35</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4">
-        <v>117.17</v>
-      </c>
-      <c r="G4">
-        <v>0.45</v>
-      </c>
-      <c r="H4">
-        <v>0.7</v>
-      </c>
-      <c r="I4">
-        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2430,28 +2527,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D5">
-        <v>119.81</v>
+        <v>107.88</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
       </c>
       <c r="F5">
-        <v>116.75</v>
+        <v>120.66</v>
       </c>
       <c r="G5">
-        <v>0.55</v>
+        <v>0.511</v>
       </c>
       <c r="H5">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2459,28 +2556,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D6">
-        <v>125.26</v>
+        <v>132.16</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F6">
-        <v>116.41</v>
+        <v>117.96</v>
       </c>
       <c r="G6">
-        <v>0.475</v>
+        <v>0.444</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2488,28 +2585,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7">
-        <v>124.9</v>
+        <v>123.32</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>116.48</v>
+        <v>118.94</v>
       </c>
       <c r="G7">
-        <v>0.525</v>
+        <v>0.511</v>
       </c>
       <c r="H7">
-        <v>-0.2</v>
+        <v>-0.6</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2517,28 +2614,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8">
-        <v>122.9</v>
+        <v>124.35</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>116.13</v>
+        <v>118.83</v>
       </c>
       <c r="G8">
-        <v>0.45</v>
+        <v>0.511</v>
       </c>
       <c r="H8">
         <v>-0.8</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2546,28 +2643,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9">
-        <v>100.34</v>
+        <v>125.44</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F9">
-        <v>116.6</v>
+        <v>118.71</v>
       </c>
       <c r="G9">
-        <v>0.525</v>
+        <v>0.467</v>
       </c>
       <c r="H9">
-        <v>-0.9</v>
+        <v>-1</v>
       </c>
       <c r="I9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2575,28 +2672,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D10">
-        <v>131.65</v>
+        <v>134.34</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F10">
-        <v>115.71</v>
+        <v>118.78</v>
       </c>
       <c r="G10">
-        <v>0.55</v>
+        <v>0.556</v>
       </c>
       <c r="H10">
-        <v>-0.9</v>
+        <v>-1</v>
       </c>
       <c r="I10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2604,28 +2701,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D11">
-        <v>101.16</v>
+        <v>110.93</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F11">
-        <v>117.54</v>
+        <v>117.38</v>
       </c>
       <c r="G11">
-        <v>0.5</v>
+        <v>0.556</v>
       </c>
       <c r="H11">
-        <v>-1.4</v>
+        <v>-2.2</v>
       </c>
       <c r="I11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -2643,28 +2740,28 @@
         <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2672,86 +2769,86 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>124.355</v>
+        <v>132.164</v>
       </c>
       <c r="E2">
-        <v>497.42</v>
+        <v>660.8199999999999</v>
       </c>
       <c r="F2">
-        <v>98.7</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C3">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="D3">
-        <v>131.645</v>
+        <v>125.44</v>
       </c>
       <c r="E3">
-        <v>526.58</v>
+        <v>627.1999999999999</v>
       </c>
       <c r="F3">
-        <v>97.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C4">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="D4">
-        <v>125.26</v>
+        <v>134.344</v>
       </c>
       <c r="E4">
-        <v>501.04</v>
+        <v>671.72</v>
       </c>
       <c r="F4">
-        <v>96.2</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2759,28 +2856,28 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C5">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="D5">
-        <v>122.9</v>
+        <v>120.548</v>
       </c>
       <c r="E5">
-        <v>491.6</v>
+        <v>602.74</v>
       </c>
       <c r="F5">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="I5" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2788,173 +2885,173 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D6">
-        <v>124.9</v>
+        <v>124.348</v>
       </c>
       <c r="E6">
-        <v>499.6</v>
+        <v>621.74</v>
       </c>
       <c r="F6">
-        <v>89.7</v>
+        <v>75</v>
       </c>
       <c r="G6">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="H6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>65</v>
       </c>
       <c r="C7">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="D7">
-        <v>119.805</v>
+        <v>123.324</v>
       </c>
       <c r="E7">
-        <v>479.22</v>
+        <v>616.62</v>
       </c>
       <c r="F7">
-        <v>60.9</v>
+        <v>70.8</v>
       </c>
       <c r="G7">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="H7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="D8">
-        <v>112.13</v>
+        <v>107.916</v>
       </c>
       <c r="E8">
-        <v>448.52</v>
+        <v>539.58</v>
       </c>
       <c r="F8">
-        <v>34.2</v>
+        <v>43</v>
       </c>
       <c r="G8">
-        <v>6.1</v>
+        <v>7.3</v>
       </c>
       <c r="H8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I8" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C9">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D9">
-        <v>101.94</v>
+        <v>107.88</v>
       </c>
       <c r="E9">
-        <v>407.76</v>
+        <v>539.4000000000001</v>
       </c>
       <c r="F9">
-        <v>17.4</v>
+        <v>19.5</v>
       </c>
       <c r="G9">
-        <v>14.6</v>
+        <v>18.7</v>
       </c>
       <c r="H9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I9" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C10">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D10">
-        <v>101.16</v>
+        <v>110.928</v>
       </c>
       <c r="E10">
-        <v>404.64</v>
+        <v>554.6400000000001</v>
       </c>
       <c r="F10">
-        <v>7.199999999999999</v>
+        <v>16.7</v>
       </c>
       <c r="G10">
-        <v>34.7</v>
+        <v>24.1</v>
       </c>
       <c r="H10" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C11">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D11">
-        <v>100.335</v>
+        <v>106.896</v>
       </c>
       <c r="E11">
-        <v>401.34</v>
+        <v>534.48</v>
       </c>
       <c r="F11">
-        <v>4.5</v>
+        <v>8.1</v>
       </c>
       <c r="G11">
-        <v>41.8</v>
+        <v>45.2</v>
       </c>
       <c r="H11" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I11" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -2972,16 +3069,16 @@
         <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2989,19 +3086,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3009,19 +3106,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3032,16 +3129,16 @@
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3049,19 +3146,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3069,19 +3166,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3089,19 +3186,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3109,19 +3206,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D8">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3129,19 +3226,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D9">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3149,19 +3246,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D10">
-        <v>-11</v>
+        <v>-13</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3169,19 +3266,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D11">
-        <v>-12</v>
+        <v>-16</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F11" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -3191,67 +3288,76 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>100</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>-1</v>
+      </c>
+      <c r="D2">
+        <v>10</v>
+      </c>
+      <c r="E2">
+        <v>11</v>
+      </c>
+      <c r="F2">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2">
+      <c r="B3">
         <v>6</v>
       </c>
-      <c r="C2">
+      <c r="C3">
         <v>6</v>
       </c>
-      <c r="D2">
+      <c r="D3">
         <v>6</v>
       </c>
-      <c r="E2">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>-1</v>
-      </c>
-      <c r="D3">
-        <v>10</v>
-      </c>
       <c r="E3">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>12</v>
+      </c>
+      <c r="F3">
+        <v>8</v>
+      </c>
+      <c r="G3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -3267,148 +3373,172 @@
       <c r="E4">
         <v>7</v>
       </c>
-      <c r="F4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="F4">
+        <v>6</v>
+      </c>
+      <c r="G4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="C5">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>-4</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="E6">
+        <v>-6</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>-7</v>
+      </c>
+      <c r="C7">
+        <v>-7</v>
+      </c>
+      <c r="D7">
         <v>1</v>
       </c>
-      <c r="F6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1" t="s">
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B7">
+      <c r="B8">
         <v>-5</v>
       </c>
-      <c r="C7">
+      <c r="C8">
         <v>-4</v>
-      </c>
-      <c r="D7">
-        <v>-1</v>
-      </c>
-      <c r="E7">
-        <v>-1</v>
-      </c>
-      <c r="F7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8">
-        <v>-4</v>
-      </c>
-      <c r="C8">
-        <v>-6</v>
       </c>
       <c r="D8">
         <v>-1</v>
       </c>
       <c r="E8">
-        <v>-4</v>
-      </c>
-      <c r="F8" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>-1</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9">
-        <v>-10</v>
+        <v>-2</v>
       </c>
       <c r="E9">
-        <v>-6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>-2</v>
+      </c>
+      <c r="G9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10">
+        <v>-1</v>
+      </c>
+      <c r="C10">
+        <v>-2</v>
+      </c>
+      <c r="D10">
+        <v>-11</v>
+      </c>
+      <c r="E10">
+        <v>-12</v>
+      </c>
+      <c r="F10">
+        <v>-13</v>
+      </c>
+      <c r="G10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>1</v>
       </c>
-      <c r="C10">
+      <c r="C11">
         <v>2</v>
       </c>
-      <c r="D10">
+      <c r="D11">
         <v>-4</v>
       </c>
-      <c r="E10">
+      <c r="E11">
         <v>-11</v>
       </c>
-      <c r="F10" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11">
-        <v>-1</v>
-      </c>
-      <c r="C11">
-        <v>-2</v>
-      </c>
-      <c r="D11">
-        <v>-11</v>
-      </c>
-      <c r="E11">
-        <v>-12</v>
-      </c>
-      <c r="F11" t="s">
-        <v>92</v>
+      <c r="F11">
+        <v>-16</v>
+      </c>
+      <c r="G11" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Brown Munde 2026.xlsx
+++ b/data/leagues/Brown Munde 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="109">
   <si>
     <t>Still Rollin'</t>
   </si>
@@ -55,19 +55,22 @@
     <t>BurgerBoyz</t>
   </si>
   <si>
-    <t>3-2-0</t>
-  </si>
-  <si>
-    <t>4-1-0</t>
-  </si>
-  <si>
-    <t>2-3-0</t>
-  </si>
-  <si>
-    <t>5-0-0</t>
-  </si>
-  <si>
-    <t>1-4-0</t>
+    <t>4-2-0</t>
+  </si>
+  <si>
+    <t>3-3-0</t>
+  </si>
+  <si>
+    <t>2-4-0</t>
+  </si>
+  <si>
+    <t>6-0-0</t>
+  </si>
+  <si>
+    <t>1-5-0</t>
+  </si>
+  <si>
+    <t>5-1-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -139,6 +142,9 @@
     <t>Week_6</t>
   </si>
   <si>
+    <t>Week_7</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -160,33 +166,33 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>KASHYAP AShok</t>
+  </si>
+  <si>
     <t>Prahlad Singh</t>
   </si>
   <si>
     <t>Kiran MADUGULA</t>
   </si>
   <si>
-    <t>KASHYAP AShok</t>
+    <t>Pawan Bhambhwani</t>
+  </si>
+  <si>
+    <t>Krishna Padodara</t>
   </si>
   <si>
     <t>suraj bhalani</t>
   </si>
   <si>
+    <t>Guruansh Singh</t>
+  </si>
+  <si>
+    <t>Harshit Aggarwal</t>
+  </si>
+  <si>
     <t>Utkarsh Gupta</t>
   </si>
   <si>
-    <t>Guruansh Singh</t>
-  </si>
-  <si>
-    <t>Harshit Aggarwal</t>
-  </si>
-  <si>
-    <t>Pawan Bhambhwani</t>
-  </si>
-  <si>
-    <t>Krishna Padodara</t>
-  </si>
-  <si>
     <t>Hark Nanda</t>
   </si>
   <si>
@@ -214,49 +220,49 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>5-0</t>
-  </si>
-  <si>
-    <t>4-1</t>
-  </si>
-  <si>
-    <t>2-3</t>
-  </si>
-  <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>1-4</t>
-  </si>
-  <si>
-    <t>10.9-3.0-0.1</t>
-  </si>
-  <si>
-    <t>9.2-4.7-0.1</t>
-  </si>
-  <si>
-    <t>7.7-6.2-0.1</t>
-  </si>
-  <si>
-    <t>7.4-6.5-0.1</t>
-  </si>
-  <si>
-    <t>7.0-6.9-0.1</t>
-  </si>
-  <si>
-    <t>6.8-7.1-0.1</t>
-  </si>
-  <si>
-    <t>6.3-7.6-0.1</t>
-  </si>
-  <si>
-    <t>5.3-8.6-0.1</t>
-  </si>
-  <si>
-    <t>4.8-9.1-0.1</t>
-  </si>
-  <si>
-    <t>4.2-9.7-0.1</t>
+    <t>6-0</t>
+  </si>
+  <si>
+    <t>5-1</t>
+  </si>
+  <si>
+    <t>4-2</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>1-5</t>
+  </si>
+  <si>
+    <t>11.2-2.7-0.1</t>
+  </si>
+  <si>
+    <t>9.0-4.9-0.1</t>
+  </si>
+  <si>
+    <t>8.4-5.5-0.1</t>
+  </si>
+  <si>
+    <t>8.0-5.9-0.1</t>
+  </si>
+  <si>
+    <t>6.9-7.0-0.1</t>
+  </si>
+  <si>
+    <t>7.3-6.6-0.1</t>
+  </si>
+  <si>
+    <t>6.2-7.7-0.1</t>
+  </si>
+  <si>
+    <t>4.9-9.0-0.1</t>
+  </si>
+  <si>
+    <t>3.9-10.1-0.1</t>
   </si>
   <si>
     <t>11-3</t>
@@ -289,28 +295,22 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↓1</t>
-  </si>
-  <si>
-    <t>↓4</t>
-  </si>
-  <si>
-    <t>↑8</t>
-  </si>
-  <si>
-    <t>↑10</t>
-  </si>
-  <si>
-    <t>↓2</t>
-  </si>
-  <si>
-    <t>↑1</t>
-  </si>
-  <si>
-    <t>↓3</t>
-  </si>
-  <si>
-    <t>↓5</t>
+    <t>↑2</t>
+  </si>
+  <si>
+    <t>↑5</t>
+  </si>
+  <si>
+    <t>↓8</t>
+  </si>
+  <si>
+    <t>↑3</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>↓10</t>
   </si>
   <si>
     <t>Week 1</t>
@@ -326,6 +326,9 @@
   </si>
   <si>
     <t>Week 5</t>
+  </si>
+  <si>
+    <t>Week 6</t>
   </si>
   <si>
     <t>Week</t>
@@ -747,16 +750,16 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
@@ -765,10 +768,10 @@
         <v>12</v>
       </c>
       <c r="I2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K2" t="s">
         <v>10</v>
@@ -779,19 +782,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
         <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
         <v>14</v>
@@ -800,10 +803,10 @@
         <v>12</v>
       </c>
       <c r="I3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K3" t="s">
         <v>12</v>
@@ -814,34 +817,34 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>11</v>
       </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
       <c r="G4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
         <v>12</v>
       </c>
       <c r="I4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J4" t="s">
         <v>10</v>
       </c>
       <c r="K4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -849,13 +852,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
@@ -864,19 +867,19 @@
         <v>10</v>
       </c>
       <c r="G5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -887,7 +890,7 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
@@ -911,7 +914,7 @@
         <v>12</v>
       </c>
       <c r="K6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -922,13 +925,13 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
@@ -940,13 +943,13 @@
         <v>12</v>
       </c>
       <c r="I7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J7" t="s">
         <v>12</v>
       </c>
       <c r="K7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -954,10 +957,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -966,7 +969,7 @@
         <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8" t="s">
         <v>12</v>
@@ -981,7 +984,7 @@
         <v>10</v>
       </c>
       <c r="K8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -989,22 +992,22 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H9" t="s">
         <v>10</v>
@@ -1013,10 +1016,10 @@
         <v>10</v>
       </c>
       <c r="J9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K9" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1024,34 +1027,34 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
         <v>11</v>
       </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
         <v>10</v>
       </c>
       <c r="H10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I10" t="s">
         <v>10</v>
       </c>
       <c r="J10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1062,25 +1065,25 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" t="s">
         <v>11</v>
       </c>
-      <c r="D11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" t="s">
-        <v>10</v>
-      </c>
       <c r="H11" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I11" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J11" t="s">
         <v>10</v>
@@ -1096,30 +1099,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1179,10 +1182,10 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -1208,22 +1211,22 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>-7</v>
+        <v>10</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1231,25 +1234,25 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>-7</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1257,22 +1260,22 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" t="s">
         <v>9</v>
       </c>
-      <c r="D7" t="s">
-        <v>8</v>
-      </c>
       <c r="E7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H7" t="s">
         <v>9</v>
@@ -1283,22 +1286,22 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s">
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E8">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>-2</v>
+        <v>6</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H8" t="s">
         <v>9</v>
@@ -1309,25 +1312,25 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E9">
+        <v>-4</v>
+      </c>
+      <c r="F9">
+        <v>-2</v>
+      </c>
+      <c r="G9">
         <v>2</v>
       </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
       <c r="H9" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1335,24 +1338,76 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10">
-        <v>-11</v>
+        <v>2</v>
       </c>
       <c r="F10">
-        <v>-10</v>
+        <v>1</v>
       </c>
       <c r="G10">
         <v>1</v>
       </c>
       <c r="H10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11">
+        <v>6</v>
+      </c>
+      <c r="F11">
+        <v>5</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12">
+        <v>-11</v>
+      </c>
+      <c r="F12">
+        <v>-10</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1368,13 +1423,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1382,13 +1437,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1396,10 +1451,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
@@ -1410,13 +1465,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1424,13 +1479,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C5">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1438,13 +1493,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1452,13 +1507,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1466,13 +1521,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1480,13 +1535,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1497,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
@@ -1511,7 +1566,7 @@
         <v>9</v>
       </c>
       <c r="C11">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="D11" t="s">
         <v>13</v>
@@ -1529,16 +1584,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1549,10 +1604,10 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="D2">
-        <v>-1.2</v>
+        <v>-1.4</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
@@ -1563,13 +1618,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D3">
-        <v>-1</v>
+        <v>0.5</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -1580,16 +1635,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C4">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="D4">
-        <v>0.7999999999999998</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1597,16 +1652,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="D5">
-        <v>0.6000000000000001</v>
+        <v>-1.7</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1614,16 +1669,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="D6">
-        <v>-0.5</v>
+        <v>1.1</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1631,13 +1686,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="D7">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
@@ -1648,16 +1703,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="D8">
-        <v>0.3999999999999999</v>
+        <v>-1.5</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1665,16 +1720,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="D9">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1682,16 +1737,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="D10">
-        <v>-1.2</v>
+        <v>1.1</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1702,10 +1757,10 @@
         <v>1</v>
       </c>
       <c r="C11">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="D11">
-        <v>0.5</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="E11" t="s">
         <v>14</v>
@@ -1723,40 +1778,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1764,28 +1819,28 @@
         <v>9</v>
       </c>
       <c r="B2">
-        <v>72.7</v>
+        <v>79.2</v>
       </c>
       <c r="C2">
-        <v>17.1</v>
+        <v>13.9</v>
       </c>
       <c r="D2">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="F2">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="G2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>0.1</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1794,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1802,227 +1857,227 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>16.7</v>
+        <v>8.4</v>
       </c>
       <c r="C3">
-        <v>35.6</v>
+        <v>30.4</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>25.5</v>
       </c>
       <c r="E3">
-        <v>12.9</v>
+        <v>14.6</v>
       </c>
       <c r="F3">
-        <v>6.1</v>
+        <v>11.2</v>
       </c>
       <c r="G3">
-        <v>3.8</v>
+        <v>6.3</v>
       </c>
       <c r="H3">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="I3">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K3">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>98.09999999999999</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4">
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
       <c r="C4">
-        <v>19</v>
+        <v>21.4</v>
       </c>
       <c r="D4">
-        <v>22.3</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>20.3</v>
+        <v>19.9</v>
       </c>
       <c r="F4">
-        <v>13.1</v>
+        <v>14.8</v>
       </c>
       <c r="G4">
-        <v>8.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H4">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="I4">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J4">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="K4">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>89.90000000000001</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>12.7</v>
+        <v>20.7</v>
       </c>
       <c r="D5">
-        <v>13.7</v>
+        <v>20.1</v>
       </c>
       <c r="E5">
-        <v>16.6</v>
+        <v>20.2</v>
       </c>
       <c r="F5">
-        <v>18.3</v>
+        <v>15.2</v>
       </c>
       <c r="G5">
-        <v>15.6</v>
+        <v>9.4</v>
       </c>
       <c r="H5">
-        <v>9.9</v>
+        <v>6.7</v>
       </c>
       <c r="I5">
-        <v>6.8</v>
+        <v>2.3</v>
       </c>
       <c r="J5">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>79</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="C6">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="D6">
-        <v>13.4</v>
+        <v>12.2</v>
       </c>
       <c r="E6">
-        <v>16.7</v>
+        <v>17.6</v>
       </c>
       <c r="F6">
-        <v>20.4</v>
+        <v>19.9</v>
       </c>
       <c r="G6">
-        <v>15.6</v>
+        <v>20.8</v>
       </c>
       <c r="H6">
-        <v>12.6</v>
+        <v>13.2</v>
       </c>
       <c r="I6">
-        <v>7.9</v>
+        <v>6.6</v>
       </c>
       <c r="J6">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="L6">
-        <v>75</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B7">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="D7">
-        <v>12.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E7">
-        <v>16.3</v>
+        <v>15.4</v>
       </c>
       <c r="F7">
-        <v>18.3</v>
+        <v>19.8</v>
       </c>
       <c r="G7">
-        <v>16.9</v>
+        <v>21.5</v>
       </c>
       <c r="H7">
-        <v>14.8</v>
+        <v>19.4</v>
       </c>
       <c r="I7">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>4.6</v>
+        <v>1.7</v>
       </c>
       <c r="K7">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="L7">
-        <v>70.8</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D8">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="E8">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="F8">
-        <v>11.3</v>
+        <v>14.6</v>
       </c>
       <c r="G8">
-        <v>17.3</v>
+        <v>20.2</v>
       </c>
       <c r="H8">
-        <v>18.5</v>
+        <v>28.2</v>
       </c>
       <c r="I8">
-        <v>17.8</v>
+        <v>14.6</v>
       </c>
       <c r="J8">
-        <v>13.4</v>
+        <v>5.6</v>
       </c>
       <c r="K8">
-        <v>7.3</v>
+        <v>2.5</v>
       </c>
       <c r="L8">
-        <v>43</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2030,37 +2085,37 @@
         <v>5</v>
       </c>
       <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
         <v>0.1</v>
       </c>
-      <c r="C9">
-        <v>0.2</v>
-      </c>
       <c r="D9">
+        <v>0.5</v>
+      </c>
+      <c r="E9">
         <v>1.7</v>
       </c>
-      <c r="E9">
-        <v>2.8</v>
-      </c>
       <c r="F9">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="G9">
-        <v>8.9</v>
+        <v>6.7</v>
       </c>
       <c r="H9">
-        <v>14.9</v>
+        <v>13.8</v>
       </c>
       <c r="I9">
-        <v>22.5</v>
+        <v>29.6</v>
       </c>
       <c r="J9">
-        <v>24.4</v>
+        <v>27.1</v>
       </c>
       <c r="K9">
-        <v>18.7</v>
+        <v>17.1</v>
       </c>
       <c r="L9">
-        <v>19.5</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -2074,31 +2129,31 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>2.9</v>
+        <v>0.1</v>
       </c>
       <c r="F10">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="G10">
-        <v>8.699999999999999</v>
+        <v>2.7</v>
       </c>
       <c r="H10">
-        <v>14.3</v>
+        <v>6.7</v>
       </c>
       <c r="I10">
-        <v>19.8</v>
+        <v>18.8</v>
       </c>
       <c r="J10">
-        <v>25.1</v>
+        <v>26.6</v>
       </c>
       <c r="K10">
-        <v>24.1</v>
+        <v>44.3</v>
       </c>
       <c r="L10">
-        <v>16.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2106,37 +2161,37 @@
         <v>1</v>
       </c>
       <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
         <v>0.1</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
       </c>
       <c r="D11">
         <v>0.2</v>
       </c>
       <c r="E11">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="F11">
-        <v>2.3</v>
+        <v>0.2</v>
       </c>
       <c r="G11">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="H11">
-        <v>7.7</v>
+        <v>6.1</v>
       </c>
       <c r="I11">
-        <v>14.6</v>
+        <v>19.3</v>
       </c>
       <c r="J11">
-        <v>24.4</v>
+        <v>36</v>
       </c>
       <c r="K11">
-        <v>45.2</v>
+        <v>35.1</v>
       </c>
       <c r="L11">
-        <v>8.1</v>
+        <v>3.5</v>
       </c>
     </row>
   </sheetData>
@@ -2146,214 +2201,241 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>38</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B2">
-        <v>72.39999999999999</v>
+        <v>72</v>
       </c>
       <c r="C2">
-        <v>94.5</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="D2">
-        <v>95.59999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="E2">
-        <v>99.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="F2">
-        <v>99.7</v>
+        <v>99.8</v>
       </c>
       <c r="G2">
-        <v>99.7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="C3">
-        <v>50.8</v>
+        <v>48.9</v>
       </c>
       <c r="D3">
-        <v>94.5</v>
+        <v>93.5</v>
       </c>
       <c r="E3">
-        <v>97</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F3">
-        <v>95.7</v>
+        <v>96.5</v>
       </c>
       <c r="G3">
-        <v>96.2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>96.3</v>
+      </c>
+      <c r="H3">
+        <v>94.69999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>8.200000000000001</v>
+      </c>
+      <c r="C4">
+        <v>43.5</v>
+      </c>
+      <c r="D4">
+        <v>55.00000000000001</v>
+      </c>
+      <c r="E4">
+        <v>95.3</v>
+      </c>
+      <c r="F4">
+        <v>81.10000000000001</v>
+      </c>
+      <c r="G4">
+        <v>93.8</v>
+      </c>
+      <c r="H4">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>100</v>
+      </c>
+      <c r="C5">
+        <v>99.8</v>
+      </c>
+      <c r="D5">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="E5">
+        <v>97.5</v>
+      </c>
+      <c r="F5">
+        <v>69.69999999999999</v>
+      </c>
+      <c r="G5">
+        <v>93.60000000000001</v>
+      </c>
+      <c r="H5">
+        <v>92.90000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4">
+      <c r="B6">
         <v>100</v>
       </c>
-      <c r="C4">
-        <v>97.8</v>
-      </c>
-      <c r="D4">
-        <v>69.39999999999999</v>
-      </c>
-      <c r="E4">
-        <v>63.5</v>
-      </c>
-      <c r="F4">
-        <v>91.8</v>
-      </c>
-      <c r="G4">
-        <v>89.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5">
-        <v>8.799999999999999</v>
-      </c>
-      <c r="C5">
-        <v>43</v>
-      </c>
-      <c r="D5">
-        <v>54</v>
-      </c>
-      <c r="E5">
-        <v>95.09999999999999</v>
-      </c>
-      <c r="F5">
-        <v>81.2</v>
-      </c>
-      <c r="G5">
-        <v>79.90000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1" t="s">
+      <c r="C6">
+        <v>98.5</v>
+      </c>
+      <c r="D6">
+        <v>69.5</v>
+      </c>
+      <c r="E6">
+        <v>62.3</v>
+      </c>
+      <c r="F6">
+        <v>91.60000000000001</v>
+      </c>
+      <c r="G6">
+        <v>77.7</v>
+      </c>
+      <c r="H6">
+        <v>77.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7">
+        <v>91.7</v>
+      </c>
+      <c r="C7">
+        <v>17.7</v>
+      </c>
+      <c r="D7">
+        <v>21.4</v>
+      </c>
+      <c r="E7">
+        <v>16</v>
+      </c>
+      <c r="F7">
+        <v>38.8</v>
+      </c>
+      <c r="G7">
+        <v>68.5</v>
+      </c>
+      <c r="H7">
+        <v>67.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B6">
-        <v>79.60000000000001</v>
-      </c>
-      <c r="C6">
-        <v>88</v>
-      </c>
-      <c r="D6">
+      <c r="B8">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="C8">
+        <v>88.2</v>
+      </c>
+      <c r="D8">
         <v>58.2</v>
       </c>
-      <c r="E6">
-        <v>88.5</v>
-      </c>
-      <c r="F6">
-        <v>75.3</v>
-      </c>
-      <c r="G6">
-        <v>77.2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>100</v>
-      </c>
-      <c r="C7">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="D7">
-        <v>98.2</v>
-      </c>
-      <c r="E7">
-        <v>96.8</v>
-      </c>
-      <c r="F7">
-        <v>69.5</v>
-      </c>
-      <c r="G7">
-        <v>72.39999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="C8">
-        <v>19.6</v>
-      </c>
-      <c r="D8">
-        <v>20.8</v>
-      </c>
       <c r="E8">
-        <v>16.6</v>
+        <v>90.3</v>
       </c>
       <c r="F8">
-        <v>39.7</v>
+        <v>75.7</v>
       </c>
       <c r="G8">
-        <v>41.09999999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>51</v>
+      </c>
+      <c r="H8">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B9">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="C9">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="D9">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="E9">
-        <v>6.600000000000001</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="F9">
-        <v>22.6</v>
+        <v>24.2</v>
       </c>
       <c r="G9">
-        <v>21.6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>12</v>
+      </c>
+      <c r="H9">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -2361,42 +2443,48 @@
         <v>12.1</v>
       </c>
       <c r="C10">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D10">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E10">
-        <v>4.100000000000001</v>
+        <v>3.6</v>
       </c>
       <c r="F10">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="G10">
-        <v>16.6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>2.7</v>
+      </c>
+      <c r="H10">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B11">
-        <v>36.6</v>
+        <v>35</v>
       </c>
       <c r="C11">
-        <v>95.39999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="D11">
-        <v>79.5</v>
+        <v>77</v>
       </c>
       <c r="E11">
-        <v>32.5</v>
+        <v>31.5</v>
       </c>
       <c r="F11">
-        <v>9.199999999999999</v>
+        <v>7.399999999999999</v>
       </c>
       <c r="G11">
-        <v>5.800000000000001</v>
+        <v>4.399999999999999</v>
+      </c>
+      <c r="H11">
+        <v>3.5</v>
       </c>
     </row>
   </sheetData>
@@ -2411,28 +2499,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2440,28 +2528,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D2">
-        <v>107.92</v>
+        <v>104.16</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>119.58</v>
+        <v>118.17</v>
       </c>
       <c r="G2">
-        <v>0.444</v>
+        <v>0.521</v>
       </c>
       <c r="H2">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2469,28 +2557,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D3">
-        <v>120.55</v>
+        <v>107.73</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3">
-        <v>122.19</v>
+        <v>115.5</v>
       </c>
       <c r="G3">
-        <v>0.467</v>
+        <v>0.458</v>
       </c>
       <c r="H3">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2498,28 +2586,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D4">
-        <v>106.9</v>
+        <v>122.55</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>120.77</v>
+        <v>117.33</v>
       </c>
       <c r="G4">
-        <v>0.533</v>
+        <v>0.458</v>
       </c>
       <c r="H4">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="I4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2527,28 +2615,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D5">
-        <v>107.88</v>
+        <v>117.38</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F5">
-        <v>120.66</v>
+        <v>117.34</v>
       </c>
       <c r="G5">
-        <v>0.511</v>
+        <v>0.5</v>
       </c>
       <c r="H5">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2556,28 +2644,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D6">
-        <v>132.16</v>
+        <v>128.3</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>117.96</v>
+        <v>115.26</v>
       </c>
       <c r="G6">
-        <v>0.444</v>
+        <v>0.521</v>
       </c>
       <c r="H6">
-        <v>0.1</v>
+        <v>-0.6</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2585,28 +2673,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7">
+        <v>102.5</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7">
+        <v>115.78</v>
+      </c>
+      <c r="G7">
+        <v>0.521</v>
+      </c>
+      <c r="H7">
+        <v>-1.1</v>
+      </c>
+      <c r="I7">
         <v>8</v>
-      </c>
-      <c r="C7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7">
-        <v>123.32</v>
-      </c>
-      <c r="E7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7">
-        <v>118.94</v>
-      </c>
-      <c r="G7">
-        <v>0.511</v>
-      </c>
-      <c r="H7">
-        <v>-0.6</v>
-      </c>
-      <c r="I7">
-        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2614,28 +2702,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D8">
-        <v>124.35</v>
+        <v>128.55</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F8">
-        <v>118.83</v>
+        <v>115.78</v>
       </c>
       <c r="G8">
-        <v>0.511</v>
+        <v>0.521</v>
       </c>
       <c r="H8">
-        <v>-0.8</v>
+        <v>-1.1</v>
       </c>
       <c r="I8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2643,28 +2731,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D9">
-        <v>125.44</v>
+        <v>116.69</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F9">
-        <v>118.71</v>
+        <v>114.75</v>
       </c>
       <c r="G9">
-        <v>0.467</v>
+        <v>0.5</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="I9">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2672,28 +2760,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D10">
-        <v>134.34</v>
+        <v>128.29</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F10">
-        <v>118.78</v>
+        <v>112.59</v>
       </c>
       <c r="G10">
-        <v>0.556</v>
+        <v>0.458</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="I10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2704,25 +2792,25 @@
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D11">
-        <v>110.93</v>
+        <v>101.13</v>
       </c>
       <c r="E11" t="s">
         <v>14</v>
       </c>
       <c r="F11">
-        <v>117.38</v>
+        <v>114.77</v>
       </c>
       <c r="G11">
-        <v>0.556</v>
+        <v>0.542</v>
       </c>
       <c r="H11">
-        <v>-2.2</v>
+        <v>-1.8</v>
       </c>
       <c r="I11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2737,31 +2825,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2769,28 +2857,28 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>132.164</v>
+        <v>128.2866666666667</v>
       </c>
       <c r="E2">
-        <v>660.8199999999999</v>
+        <v>769.7199999999999</v>
       </c>
       <c r="F2">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2798,173 +2886,173 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C3">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D3">
-        <v>125.44</v>
+        <v>117.3833333333333</v>
       </c>
       <c r="E3">
-        <v>627.1999999999999</v>
+        <v>704.3</v>
       </c>
       <c r="F3">
-        <v>98.09999999999999</v>
+        <v>96.39999999999999</v>
       </c>
       <c r="G3">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C4">
-        <v>0.4</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D4">
-        <v>134.344</v>
+        <v>122.5466666666667</v>
       </c>
       <c r="E4">
-        <v>671.72</v>
+        <v>735.28</v>
       </c>
       <c r="F4">
-        <v>89.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="G4">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C5">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D5">
-        <v>120.548</v>
+        <v>128.55</v>
       </c>
       <c r="E5">
-        <v>602.74</v>
+        <v>771.3</v>
       </c>
       <c r="F5">
-        <v>79</v>
+        <v>90.60000000000001</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C6">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="D6">
+        <v>128.3</v>
+      </c>
+      <c r="E6">
+        <v>769.8000000000001</v>
+      </c>
+      <c r="F6">
+        <v>77.8</v>
+      </c>
+      <c r="G6">
         <v>0.4</v>
       </c>
-      <c r="D6">
-        <v>124.348</v>
-      </c>
-      <c r="E6">
-        <v>621.74</v>
-      </c>
-      <c r="F6">
+      <c r="H6" t="s">
         <v>75</v>
       </c>
-      <c r="G6">
-        <v>1.1</v>
-      </c>
-      <c r="H6" t="s">
-        <v>72</v>
-      </c>
       <c r="I6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C7">
-        <v>0.4</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D7">
-        <v>123.324</v>
+        <v>107.7266666666667</v>
       </c>
       <c r="E7">
-        <v>616.62</v>
+        <v>646.36</v>
       </c>
       <c r="F7">
-        <v>70.8</v>
+        <v>71.3</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="H7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C8">
-        <v>0.6</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D8">
-        <v>107.916</v>
+        <v>116.6933333333333</v>
       </c>
       <c r="E8">
-        <v>539.58</v>
+        <v>700.16</v>
       </c>
       <c r="F8">
-        <v>43</v>
+        <v>49.1</v>
       </c>
       <c r="G8">
-        <v>7.3</v>
+        <v>2.5</v>
       </c>
       <c r="H8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2972,28 +3060,28 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C9">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D9">
-        <v>107.88</v>
+        <v>102.5</v>
       </c>
       <c r="E9">
-        <v>539.4000000000001</v>
+        <v>615.0000000000001</v>
       </c>
       <c r="F9">
-        <v>19.5</v>
+        <v>12.4</v>
       </c>
       <c r="G9">
-        <v>18.7</v>
+        <v>17.1</v>
       </c>
       <c r="H9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3001,28 +3089,28 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C10">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="D10">
-        <v>110.928</v>
+        <v>101.13</v>
       </c>
       <c r="E10">
-        <v>554.6400000000001</v>
+        <v>606.7800000000001</v>
       </c>
       <c r="F10">
-        <v>16.7</v>
+        <v>3.6</v>
       </c>
       <c r="G10">
-        <v>24.1</v>
+        <v>44.3</v>
       </c>
       <c r="H10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I10" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3030,28 +3118,28 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C11">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="D11">
-        <v>106.896</v>
+        <v>104.1566666666667</v>
       </c>
       <c r="E11">
-        <v>534.48</v>
+        <v>624.9400000000001</v>
       </c>
       <c r="F11">
-        <v>8.1</v>
+        <v>3.5</v>
       </c>
       <c r="G11">
-        <v>45.2</v>
+        <v>35.09999999999999</v>
       </c>
       <c r="H11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -3066,19 +3154,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3086,19 +3174,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D2">
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3106,19 +3194,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D3">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3126,10 +3214,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D4">
         <v>6</v>
@@ -3138,7 +3226,7 @@
         <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3146,19 +3234,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3166,19 +3254,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3186,19 +3274,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3206,19 +3294,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3226,19 +3314,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D9">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3249,16 +3337,16 @@
         <v>0</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D10">
-        <v>-13</v>
+        <v>-11</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3278,7 +3366,7 @@
         <v>14</v>
       </c>
       <c r="F11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -3288,10 +3376,10 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
         <v>96</v>
       </c>
@@ -3308,194 +3396,221 @@
         <v>100</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>101</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>10</v>
-      </c>
-      <c r="G2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>8</v>
+      </c>
+      <c r="G2">
+        <v>10</v>
+      </c>
+      <c r="H2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B3">
+        <v>8</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>12</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3">
         <v>6</v>
       </c>
-      <c r="C3">
+      <c r="G3">
+        <v>8</v>
+      </c>
+      <c r="H3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D3">
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>-10</v>
+      </c>
+      <c r="E4">
+        <v>-6</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4">
         <v>6</v>
       </c>
-      <c r="E3">
-        <v>12</v>
-      </c>
-      <c r="F3">
-        <v>8</v>
-      </c>
-      <c r="G3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>8</v>
-      </c>
-      <c r="C4">
-        <v>10</v>
-      </c>
-      <c r="D4">
-        <v>12</v>
-      </c>
-      <c r="E4">
-        <v>7</v>
-      </c>
-      <c r="F4">
-        <v>6</v>
-      </c>
-      <c r="G4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="H4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B5">
+        <v>-5</v>
+      </c>
+      <c r="C5">
         <v>-4</v>
-      </c>
-      <c r="C5">
-        <v>-6</v>
       </c>
       <c r="D5">
         <v>-1</v>
       </c>
       <c r="E5">
+        <v>-1</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>-1</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>-2</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>-2</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>-2</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>-7</v>
+      </c>
+      <c r="C8">
+        <v>-7</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9">
         <v>-4</v>
       </c>
-      <c r="F5">
+      <c r="C9">
+        <v>-6</v>
+      </c>
+      <c r="D9">
+        <v>-1</v>
+      </c>
+      <c r="E9">
+        <v>-4</v>
+      </c>
+      <c r="F9">
         <v>4</v>
       </c>
-      <c r="G5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>-10</v>
-      </c>
-      <c r="E6">
+      <c r="G9">
         <v>-6</v>
       </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>-7</v>
-      </c>
-      <c r="C7">
-        <v>-7</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>-5</v>
-      </c>
-      <c r="C8">
-        <v>-4</v>
-      </c>
-      <c r="D8">
-        <v>-1</v>
-      </c>
-      <c r="E8">
-        <v>-1</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>-2</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>-2</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>-2</v>
-      </c>
-      <c r="G9" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="H9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -3514,11 +3629,14 @@
       <c r="F10">
         <v>-13</v>
       </c>
-      <c r="G10" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="G10">
+        <v>-11</v>
+      </c>
+      <c r="H10" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
@@ -3537,8 +3655,11 @@
       <c r="F11">
         <v>-16</v>
       </c>
-      <c r="G11" t="s">
-        <v>95</v>
+      <c r="G11">
+        <v>-16</v>
+      </c>
+      <c r="H11" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Brown Munde 2026.xlsx
+++ b/data/leagues/Brown Munde 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="113">
   <si>
     <t>Still Rollin'</t>
   </si>
@@ -55,22 +55,25 @@
     <t>BurgerBoyz</t>
   </si>
   <si>
-    <t>4-2-0</t>
-  </si>
-  <si>
-    <t>3-3-0</t>
-  </si>
-  <si>
-    <t>2-4-0</t>
-  </si>
-  <si>
-    <t>6-0-0</t>
-  </si>
-  <si>
-    <t>1-5-0</t>
-  </si>
-  <si>
-    <t>5-1-0</t>
+    <t>5-2-0</t>
+  </si>
+  <si>
+    <t>3-4-0</t>
+  </si>
+  <si>
+    <t>4-3-0</t>
+  </si>
+  <si>
+    <t>2-5-0</t>
+  </si>
+  <si>
+    <t>7-0-0</t>
+  </si>
+  <si>
+    <t>1-6-0</t>
+  </si>
+  <si>
+    <t>6-1-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -145,6 +148,9 @@
     <t>Week_7</t>
   </si>
   <si>
+    <t>Week_8</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -169,33 +175,33 @@
     <t>KASHYAP AShok</t>
   </si>
   <si>
+    <t>Kiran MADUGULA</t>
+  </si>
+  <si>
     <t>Prahlad Singh</t>
   </si>
   <si>
-    <t>Kiran MADUGULA</t>
-  </si>
-  <si>
     <t>Pawan Bhambhwani</t>
   </si>
   <si>
+    <t>Harshit Aggarwal</t>
+  </si>
+  <si>
+    <t>Hark Nanda</t>
+  </si>
+  <si>
+    <t>Utkarsh Gupta</t>
+  </si>
+  <si>
+    <t>suraj bhalani</t>
+  </si>
+  <si>
     <t>Krishna Padodara</t>
   </si>
   <si>
-    <t>suraj bhalani</t>
-  </si>
-  <si>
     <t>Guruansh Singh</t>
   </si>
   <si>
-    <t>Harshit Aggarwal</t>
-  </si>
-  <si>
-    <t>Utkarsh Gupta</t>
-  </si>
-  <si>
-    <t>Hark Nanda</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -220,52 +226,52 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>6-0</t>
-  </si>
-  <si>
-    <t>5-1</t>
-  </si>
-  <si>
-    <t>4-2</t>
-  </si>
-  <si>
-    <t>3-3</t>
-  </si>
-  <si>
-    <t>2-4</t>
-  </si>
-  <si>
-    <t>1-5</t>
-  </si>
-  <si>
-    <t>11.2-2.7-0.1</t>
-  </si>
-  <si>
-    <t>9.0-4.9-0.1</t>
-  </si>
-  <si>
-    <t>8.4-5.5-0.1</t>
-  </si>
-  <si>
-    <t>8.0-5.9-0.1</t>
-  </si>
-  <si>
-    <t>6.9-7.0-0.1</t>
-  </si>
-  <si>
-    <t>7.3-6.6-0.1</t>
-  </si>
-  <si>
-    <t>6.2-7.7-0.1</t>
-  </si>
-  <si>
-    <t>4.9-9.0-0.1</t>
-  </si>
-  <si>
-    <t>3.9-10.1-0.1</t>
-  </si>
-  <si>
-    <t>11-3</t>
+    <t>7-0</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>5-2</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>2-5</t>
+  </si>
+  <si>
+    <t>1-6</t>
+  </si>
+  <si>
+    <t>11.6-2.3-0.1</t>
+  </si>
+  <si>
+    <t>8.7-5.3-0.1</t>
+  </si>
+  <si>
+    <t>8.3-5.6-0.1</t>
+  </si>
+  <si>
+    <t>8.2-5.7-0.1</t>
+  </si>
+  <si>
+    <t>6.7-7.2-0.1</t>
+  </si>
+  <si>
+    <t>6.0-7.9-0.1</t>
+  </si>
+  <si>
+    <t>4.7-9.3-0.1</t>
+  </si>
+  <si>
+    <t>3.4-10.6-0.1</t>
+  </si>
+  <si>
+    <t>3.4-10.5-0.1</t>
+  </si>
+  <si>
+    <t>12-2</t>
   </si>
   <si>
     <t>9-5</t>
@@ -280,12 +286,12 @@
     <t>6-8</t>
   </si>
   <si>
-    <t>5-9</t>
-  </si>
-  <si>
     <t>4-10</t>
   </si>
   <si>
+    <t>3-11</t>
+  </si>
+  <si>
     <t>Owners</t>
   </si>
   <si>
@@ -295,22 +301,25 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>↑1</t>
+  </si>
+  <si>
     <t>↑2</t>
   </si>
   <si>
-    <t>↑5</t>
-  </si>
-  <si>
-    <t>↓8</t>
-  </si>
-  <si>
-    <t>↑3</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>↓10</t>
+    <t>↓1</t>
+  </si>
+  <si>
+    <t>↑4</t>
+  </si>
+  <si>
+    <t>↓3</t>
+  </si>
+  <si>
+    <t>↑6</t>
+  </si>
+  <si>
+    <t>↓4</t>
   </si>
   <si>
     <t>Week 1</t>
@@ -329,6 +338,9 @@
   </si>
   <si>
     <t>Week 6</t>
+  </si>
+  <si>
+    <t>Week 7</t>
   </si>
   <si>
     <t>Week</t>
@@ -750,28 +762,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" t="s">
-        <v>11</v>
-      </c>
       <c r="J2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K2" t="s">
         <v>10</v>
@@ -785,31 +797,31 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -817,34 +829,34 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K4" t="s">
         <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" t="s">
-        <v>11</v>
-      </c>
-      <c r="J4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -855,28 +867,28 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" t="s">
         <v>12</v>
       </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" t="s">
-        <v>11</v>
-      </c>
       <c r="J5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K5" t="s">
         <v>10</v>
@@ -887,31 +899,31 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K6" t="s">
         <v>10</v>
@@ -922,31 +934,31 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" t="s">
         <v>12</v>
       </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" t="s">
-        <v>11</v>
-      </c>
       <c r="J7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K7" t="s">
         <v>10</v>
@@ -960,31 +972,31 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F8" t="s">
         <v>11</v>
       </c>
       <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" t="s">
         <v>12</v>
       </c>
-      <c r="H8" t="s">
+      <c r="J8" t="s">
         <v>12</v>
       </c>
-      <c r="I8" t="s">
-        <v>10</v>
-      </c>
-      <c r="J8" t="s">
-        <v>10</v>
-      </c>
       <c r="K8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -995,31 +1007,31 @@
         <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
         <v>12</v>
       </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>11</v>
       </c>
       <c r="H9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I9" t="s">
         <v>10</v>
       </c>
       <c r="J9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1027,34 +1039,34 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" t="s">
         <v>12</v>
       </c>
-      <c r="G10" t="s">
-        <v>10</v>
-      </c>
-      <c r="H10" t="s">
-        <v>11</v>
-      </c>
       <c r="I10" t="s">
         <v>10</v>
       </c>
       <c r="J10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1062,10 +1074,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D11" t="s">
         <v>10</v>
@@ -1080,16 +1092,16 @@
         <v>11</v>
       </c>
       <c r="H11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J11" t="s">
         <v>10</v>
       </c>
       <c r="K11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1099,30 +1111,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1182,10 +1194,10 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -1208,10 +1220,10 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
@@ -1234,25 +1246,25 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>-7</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1260,25 +1272,25 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>-7</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1286,22 +1298,22 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" t="s">
         <v>9</v>
       </c>
-      <c r="D8" t="s">
-        <v>8</v>
-      </c>
       <c r="E8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H8" t="s">
         <v>9</v>
@@ -1312,22 +1324,22 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C9" t="s">
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E9">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>-2</v>
+        <v>6</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H9" t="s">
         <v>9</v>
@@ -1338,77 +1350,25 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E10">
+        <v>-4</v>
+      </c>
+      <c r="F10">
+        <v>-2</v>
+      </c>
+      <c r="G10">
         <v>2</v>
       </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
       <c r="H10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="1">
         <v>9</v>
-      </c>
-      <c r="B11">
-        <v>6</v>
-      </c>
-      <c r="C11" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11">
-        <v>6</v>
-      </c>
-      <c r="F11">
-        <v>5</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12">
-        <v>3</v>
-      </c>
-      <c r="C12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12">
-        <v>-11</v>
-      </c>
-      <c r="F12">
-        <v>-10</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-      <c r="H12" t="s">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1423,13 +1383,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1437,13 +1397,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1451,13 +1411,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1465,13 +1425,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1479,13 +1439,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1493,13 +1453,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1510,10 +1470,10 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1521,13 +1481,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C8">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1535,10 +1495,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -1549,10 +1509,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
@@ -1566,10 +1526,10 @@
         <v>9</v>
       </c>
       <c r="C11">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1584,16 +1544,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1604,13 +1564,13 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="D2">
-        <v>-1.4</v>
+        <v>-1.7</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1621,13 +1581,13 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D3">
         <v>0.5</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1638,10 +1598,10 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="D4">
-        <v>-0.6000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -1652,16 +1612,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="D5">
-        <v>-1.7</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1669,16 +1629,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="D6">
-        <v>1.1</v>
+        <v>-1.6</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1686,16 +1646,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="D7">
-        <v>1.1</v>
+        <v>-1.6</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1703,16 +1663,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="D8">
-        <v>-1.5</v>
+        <v>1.1</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1723,13 +1683,13 @@
         <v>5</v>
       </c>
       <c r="C9">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D9">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1740,13 +1700,13 @@
         <v>4</v>
       </c>
       <c r="C10">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="D10">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1757,13 +1717,13 @@
         <v>1</v>
       </c>
       <c r="C11">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="D11">
-        <v>0.8999999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1778,40 +1738,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1819,16 +1779,16 @@
         <v>9</v>
       </c>
       <c r="B2">
-        <v>79.2</v>
+        <v>85.3</v>
       </c>
       <c r="C2">
-        <v>13.9</v>
+        <v>11.5</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="E2">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="F2">
         <v>0.1</v>
@@ -1837,10 +1797,10 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1849,45 +1809,45 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>99.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B3">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="C3">
-        <v>30.4</v>
+        <v>34.3</v>
       </c>
       <c r="D3">
-        <v>25.5</v>
+        <v>22.4</v>
       </c>
       <c r="E3">
-        <v>14.6</v>
+        <v>17.2</v>
       </c>
       <c r="F3">
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
       <c r="G3">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="H3">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="I3">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>96.40000000000001</v>
+        <v>98.09999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1895,189 +1855,189 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="C4">
-        <v>21.4</v>
+        <v>25.4</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>25.1</v>
       </c>
       <c r="E4">
-        <v>19.9</v>
+        <v>18.6</v>
       </c>
       <c r="F4">
-        <v>14.8</v>
+        <v>14.4</v>
       </c>
       <c r="G4">
-        <v>9.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="H4">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="I4">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J4">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>95.5</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="C5">
-        <v>20.7</v>
+        <v>13</v>
       </c>
       <c r="D5">
+        <v>19.4</v>
+      </c>
+      <c r="E5">
+        <v>22.2</v>
+      </c>
+      <c r="F5">
         <v>20.1</v>
       </c>
-      <c r="E5">
-        <v>20.2</v>
-      </c>
-      <c r="F5">
-        <v>15.2</v>
-      </c>
       <c r="G5">
-        <v>9.4</v>
+        <v>13.6</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>9</v>
       </c>
       <c r="I5">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J5">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>90.59999999999999</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B6">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="C6">
-        <v>6.2</v>
+        <v>12.3</v>
       </c>
       <c r="D6">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="E6">
-        <v>17.6</v>
+        <v>21.2</v>
       </c>
       <c r="F6">
-        <v>19.9</v>
+        <v>19.5</v>
       </c>
       <c r="G6">
-        <v>20.8</v>
+        <v>15.7</v>
       </c>
       <c r="H6">
-        <v>13.2</v>
+        <v>8.5</v>
       </c>
       <c r="I6">
-        <v>6.6</v>
+        <v>1.5</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="K6">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>77.8</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B7">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="C7">
-        <v>5.7</v>
+        <v>2.6</v>
       </c>
       <c r="D7">
-        <v>8.199999999999999</v>
+        <v>6.1</v>
       </c>
       <c r="E7">
-        <v>15.4</v>
+        <v>12.8</v>
       </c>
       <c r="F7">
-        <v>19.8</v>
+        <v>18.6</v>
       </c>
       <c r="G7">
-        <v>21.5</v>
+        <v>28.3</v>
       </c>
       <c r="H7">
-        <v>19.4</v>
+        <v>22.9</v>
       </c>
       <c r="I7">
         <v>7</v>
       </c>
       <c r="J7">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="K7">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>71.3</v>
+        <v>68.59999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="D8">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="E8">
-        <v>8.5</v>
+        <v>6.1</v>
       </c>
       <c r="F8">
         <v>14.6</v>
       </c>
       <c r="G8">
-        <v>20.2</v>
+        <v>22.5</v>
       </c>
       <c r="H8">
-        <v>28.2</v>
+        <v>32.4</v>
       </c>
       <c r="I8">
-        <v>14.6</v>
+        <v>13.5</v>
       </c>
       <c r="J8">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="K8">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="L8">
-        <v>49.1</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2088,34 +2048,34 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E9">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="F9">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="G9">
-        <v>6.7</v>
+        <v>5.6</v>
       </c>
       <c r="H9">
-        <v>13.8</v>
+        <v>14.1</v>
       </c>
       <c r="I9">
-        <v>29.6</v>
+        <v>40.4</v>
       </c>
       <c r="J9">
-        <v>27.1</v>
+        <v>26</v>
       </c>
       <c r="K9">
-        <v>17.1</v>
+        <v>11</v>
       </c>
       <c r="L9">
-        <v>12.4</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -2135,25 +2095,25 @@
         <v>0.1</v>
       </c>
       <c r="F10">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="G10">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>6.7</v>
+        <v>2.3</v>
       </c>
       <c r="I10">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="J10">
-        <v>26.6</v>
+        <v>29.9</v>
       </c>
       <c r="K10">
-        <v>44.3</v>
+        <v>48.2</v>
       </c>
       <c r="L10">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2164,34 +2124,34 @@
         <v>0</v>
       </c>
       <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
         <v>0.1</v>
       </c>
-      <c r="D11">
-        <v>0.2</v>
-      </c>
-      <c r="E11">
-        <v>0.4</v>
-      </c>
-      <c r="F11">
-        <v>0.2</v>
-      </c>
       <c r="G11">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="H11">
-        <v>6.1</v>
+        <v>4</v>
       </c>
       <c r="I11">
-        <v>19.3</v>
+        <v>17.8</v>
       </c>
       <c r="J11">
-        <v>36</v>
+        <v>37.6</v>
       </c>
       <c r="K11">
-        <v>35.1</v>
+        <v>39.9</v>
       </c>
       <c r="L11">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -2201,290 +2161,323 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B2">
-        <v>72</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C2">
-        <v>95.59999999999999</v>
+        <v>94.19999999999999</v>
       </c>
       <c r="D2">
-        <v>95.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="E2">
-        <v>99.40000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="F2">
         <v>99.8</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="H2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B3">
         <v>100</v>
       </c>
       <c r="C3">
-        <v>48.9</v>
+        <v>99.8</v>
       </c>
       <c r="D3">
-        <v>93.5</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="E3">
-        <v>97.09999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="F3">
-        <v>96.5</v>
+        <v>70.7</v>
       </c>
       <c r="G3">
-        <v>96.3</v>
+        <v>93.7</v>
       </c>
       <c r="H3">
-        <v>94.69999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>98.3</v>
+      </c>
+      <c r="I3">
+        <v>98.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B4">
-        <v>8.200000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="C4">
-        <v>43.5</v>
+        <v>44.2</v>
       </c>
       <c r="D4">
-        <v>55.00000000000001</v>
+        <v>52.8</v>
       </c>
       <c r="E4">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="F4">
+        <v>81.8</v>
+      </c>
+      <c r="G4">
+        <v>94.8</v>
+      </c>
+      <c r="H4">
         <v>95.3</v>
       </c>
-      <c r="F4">
-        <v>81.10000000000001</v>
-      </c>
-      <c r="G4">
-        <v>93.8</v>
-      </c>
-      <c r="H4">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4">
+        <v>95.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B5">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="C5">
+        <v>49.5</v>
+      </c>
+      <c r="D5">
+        <v>95.39999999999999</v>
+      </c>
+      <c r="E5">
+        <v>97.2</v>
+      </c>
+      <c r="F5">
+        <v>95.89999999999999</v>
+      </c>
+      <c r="G5">
+        <v>95.39999999999999</v>
+      </c>
+      <c r="H5">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="I5">
+        <v>90.40000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6">
+        <v>92</v>
+      </c>
+      <c r="C6">
+        <v>17.2</v>
+      </c>
+      <c r="D6">
+        <v>20</v>
+      </c>
+      <c r="E6">
+        <v>18.1</v>
+      </c>
+      <c r="F6">
+        <v>36</v>
+      </c>
+      <c r="G6">
+        <v>73</v>
+      </c>
+      <c r="H6">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="I6">
+        <v>89.90000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>78.60000000000001</v>
+      </c>
+      <c r="C7">
+        <v>88</v>
+      </c>
+      <c r="D7">
+        <v>62.4</v>
+      </c>
+      <c r="E7">
+        <v>91.10000000000001</v>
+      </c>
+      <c r="F7">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="G7">
+        <v>45.8</v>
+      </c>
+      <c r="H7">
+        <v>72.8</v>
+      </c>
+      <c r="I7">
+        <v>67.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8">
         <v>100</v>
       </c>
-      <c r="C5">
-        <v>99.8</v>
-      </c>
-      <c r="D5">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="E5">
-        <v>97.5</v>
-      </c>
-      <c r="F5">
-        <v>69.69999999999999</v>
-      </c>
-      <c r="G5">
-        <v>93.60000000000001</v>
-      </c>
-      <c r="H5">
-        <v>92.90000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>100</v>
-      </c>
-      <c r="C6">
-        <v>98.5</v>
-      </c>
-      <c r="D6">
-        <v>69.5</v>
-      </c>
-      <c r="E6">
-        <v>62.3</v>
-      </c>
-      <c r="F6">
-        <v>91.60000000000001</v>
-      </c>
-      <c r="G6">
-        <v>77.7</v>
-      </c>
-      <c r="H6">
-        <v>77.7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7">
-        <v>91.7</v>
-      </c>
-      <c r="C7">
-        <v>17.7</v>
-      </c>
-      <c r="D7">
-        <v>21.4</v>
-      </c>
-      <c r="E7">
-        <v>16</v>
-      </c>
-      <c r="F7">
-        <v>38.8</v>
-      </c>
-      <c r="G7">
-        <v>68.5</v>
-      </c>
-      <c r="H7">
-        <v>67.7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8">
-        <v>80.90000000000001</v>
-      </c>
       <c r="C8">
-        <v>88.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="D8">
-        <v>58.2</v>
+        <v>69.39999999999999</v>
       </c>
       <c r="E8">
-        <v>90.3</v>
+        <v>61.4</v>
       </c>
       <c r="F8">
-        <v>75.7</v>
+        <v>90.7</v>
       </c>
       <c r="G8">
-        <v>51</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="H8">
-        <v>50.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>45.3</v>
+      </c>
+      <c r="I8">
+        <v>48.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B9">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C9">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D9">
-        <v>16.5</v>
+        <v>14.9</v>
       </c>
       <c r="E9">
-        <v>7.000000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="F9">
-        <v>24.2</v>
+        <v>24</v>
       </c>
       <c r="G9">
-        <v>12</v>
+        <v>11.1</v>
       </c>
       <c r="H9">
-        <v>14.3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>9</v>
+      </c>
+      <c r="I9">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B10">
-        <v>12.1</v>
+        <v>11.7</v>
       </c>
       <c r="C10">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="D10">
-        <v>16.7</v>
+        <v>13.7</v>
       </c>
       <c r="E10">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="F10">
-        <v>15.2</v>
+        <v>17.3</v>
       </c>
       <c r="G10">
-        <v>2.7</v>
+        <v>4.399999999999999</v>
       </c>
       <c r="H10">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>0.6</v>
+      </c>
+      <c r="I10">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B11">
-        <v>35</v>
+        <v>37.2</v>
       </c>
       <c r="C11">
-        <v>95.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="D11">
-        <v>77</v>
+        <v>78.3</v>
       </c>
       <c r="E11">
-        <v>31.5</v>
+        <v>28.8</v>
       </c>
       <c r="F11">
-        <v>7.399999999999999</v>
+        <v>8.200000000000001</v>
       </c>
       <c r="G11">
-        <v>4.399999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="H11">
-        <v>3.5</v>
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="I11">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -2499,28 +2492,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2531,25 +2524,25 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D2">
-        <v>104.16</v>
+        <v>101.48</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>118.17</v>
+        <v>116.42</v>
       </c>
       <c r="G2">
-        <v>0.521</v>
+        <v>0.531</v>
       </c>
       <c r="H2">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2557,28 +2550,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D3">
-        <v>107.73</v>
+        <v>119.47</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3">
-        <v>115.5</v>
+        <v>117.02</v>
       </c>
       <c r="G3">
-        <v>0.458</v>
+        <v>0.469</v>
       </c>
       <c r="H3">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2586,28 +2579,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4">
+        <v>113.05</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4">
+        <v>115.8</v>
+      </c>
+      <c r="G4">
+        <v>0.469</v>
+      </c>
+      <c r="H4">
+        <v>1.3</v>
+      </c>
+      <c r="I4">
         <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4">
-        <v>122.55</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4">
-        <v>117.33</v>
-      </c>
-      <c r="G4">
-        <v>0.458</v>
-      </c>
-      <c r="H4">
-        <v>0.6</v>
-      </c>
-      <c r="I4">
-        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2618,25 +2611,25 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D5">
-        <v>117.38</v>
+        <v>112.02</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>117.34</v>
+        <v>115.74</v>
       </c>
       <c r="G5">
-        <v>0.5</v>
+        <v>0.449</v>
       </c>
       <c r="H5">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2644,28 +2637,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D6">
-        <v>128.3</v>
+        <v>119.87</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>115.26</v>
+        <v>115.51</v>
       </c>
       <c r="G6">
-        <v>0.521</v>
+        <v>0.531</v>
       </c>
       <c r="H6">
-        <v>-0.6</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2673,28 +2666,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D7">
-        <v>102.5</v>
+        <v>99.06</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F7">
-        <v>115.78</v>
+        <v>115.81</v>
       </c>
       <c r="G7">
-        <v>0.521</v>
+        <v>0.551</v>
       </c>
       <c r="H7">
-        <v>-1.1</v>
+        <v>0.3</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2702,28 +2695,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D8">
-        <v>128.55</v>
+        <v>128.13</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F8">
-        <v>115.78</v>
+        <v>112.57</v>
       </c>
       <c r="G8">
-        <v>0.521</v>
+        <v>0.429</v>
       </c>
       <c r="H8">
-        <v>-1.1</v>
+        <v>-1</v>
       </c>
       <c r="I8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2731,28 +2724,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D9">
-        <v>116.69</v>
+        <v>103.85</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F9">
-        <v>114.75</v>
+        <v>114.46</v>
       </c>
       <c r="G9">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="H9">
-        <v>-1.5</v>
+        <v>-1.1</v>
       </c>
       <c r="I9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2760,28 +2753,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D10">
-        <v>128.29</v>
+        <v>121.23</v>
       </c>
       <c r="E10" t="s">
         <v>13</v>
       </c>
       <c r="F10">
-        <v>112.59</v>
+        <v>112.74</v>
       </c>
       <c r="G10">
-        <v>0.458</v>
+        <v>0.531</v>
       </c>
       <c r="H10">
-        <v>-1.5</v>
+        <v>-1.1</v>
       </c>
       <c r="I10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2789,28 +2782,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D11">
-        <v>101.13</v>
+        <v>131.22</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F11">
-        <v>114.77</v>
+        <v>113.3</v>
       </c>
       <c r="G11">
-        <v>0.542</v>
+        <v>0.551</v>
       </c>
       <c r="H11">
-        <v>-1.8</v>
+        <v>-2.6</v>
       </c>
       <c r="I11">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2825,31 +2818,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2857,57 +2850,57 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>128.2866666666667</v>
+        <v>128.1285714285714</v>
       </c>
       <c r="E2">
-        <v>769.7199999999999</v>
+        <v>896.8999999999999</v>
       </c>
       <c r="F2">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C3">
-        <v>0.8333333333333334</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D3">
-        <v>117.3833333333333</v>
+        <v>131.2171428571428</v>
       </c>
       <c r="E3">
-        <v>704.3</v>
+        <v>918.52</v>
       </c>
       <c r="F3">
-        <v>96.39999999999999</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2915,144 +2908,144 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C4">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D4">
-        <v>122.5466666666667</v>
+        <v>119.4714285714286</v>
       </c>
       <c r="E4">
-        <v>735.28</v>
+        <v>836.3</v>
       </c>
       <c r="F4">
-        <v>95.5</v>
+        <v>94.3</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C5">
-        <v>0.5</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D5">
-        <v>128.55</v>
+        <v>113.0514285714286</v>
       </c>
       <c r="E5">
-        <v>771.3</v>
+        <v>791.36</v>
       </c>
       <c r="F5">
-        <v>90.60000000000001</v>
+        <v>90</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
       </c>
       <c r="C6">
-        <v>0.3333333333333333</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D6">
-        <v>128.3</v>
+        <v>112.0171428571428</v>
       </c>
       <c r="E6">
-        <v>769.8000000000001</v>
+        <v>784.1199999999999</v>
       </c>
       <c r="F6">
-        <v>77.8</v>
+        <v>89.60000000000001</v>
       </c>
       <c r="G6">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C7">
-        <v>0.6666666666666666</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D7">
-        <v>107.7266666666667</v>
+        <v>119.8685714285714</v>
       </c>
       <c r="E7">
-        <v>646.36</v>
+        <v>839.0799999999999</v>
       </c>
       <c r="F7">
-        <v>71.3</v>
+        <v>68.60000000000001</v>
       </c>
       <c r="G7">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C8">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D8">
-        <v>116.6933333333333</v>
+        <v>121.2257142857143</v>
       </c>
       <c r="E8">
-        <v>700.16</v>
+        <v>848.58</v>
       </c>
       <c r="F8">
-        <v>49.1</v>
+        <v>48.7</v>
       </c>
       <c r="G8">
-        <v>2.5</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="H8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3060,28 +3053,28 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C9">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D9">
-        <v>102.5</v>
+        <v>103.8485714285714</v>
       </c>
       <c r="E9">
-        <v>615.0000000000001</v>
+        <v>726.9400000000001</v>
       </c>
       <c r="F9">
-        <v>12.4</v>
+        <v>8.5</v>
       </c>
       <c r="G9">
-        <v>17.1</v>
+        <v>11</v>
       </c>
       <c r="H9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3089,28 +3082,28 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C10">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D10">
-        <v>101.13</v>
+        <v>99.06285714285715</v>
       </c>
       <c r="E10">
-        <v>606.7800000000001</v>
+        <v>693.4400000000001</v>
       </c>
       <c r="F10">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="G10">
-        <v>44.3</v>
+        <v>48.2</v>
       </c>
       <c r="H10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3118,28 +3111,28 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C11">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D11">
-        <v>104.1566666666667</v>
+        <v>101.48</v>
       </c>
       <c r="E11">
-        <v>624.9400000000001</v>
+        <v>710.36</v>
       </c>
       <c r="F11">
-        <v>3.5</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="G11">
-        <v>35.09999999999999</v>
+        <v>39.90000000000001</v>
       </c>
       <c r="H11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -3154,19 +3147,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3177,16 +3170,16 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3197,16 +3190,16 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3217,16 +3210,16 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3240,13 +3233,13 @@
         <v>55</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3254,19 +3247,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3277,16 +3270,16 @@
         <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3294,19 +3287,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
         <v>52</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3314,19 +3307,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D9">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3334,19 +3327,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D10">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F10" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3357,13 +3350,13 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D11">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F11" t="s">
         <v>94</v>
@@ -3376,33 +3369,36 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>105</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -3424,11 +3420,14 @@
       <c r="G2">
         <v>10</v>
       </c>
-      <c r="H2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="H2">
+        <v>11</v>
+      </c>
+      <c r="I2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -3450,11 +3449,14 @@
       <c r="G3">
         <v>8</v>
       </c>
-      <c r="H3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="H3">
+        <v>10</v>
+      </c>
+      <c r="I3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -3476,11 +3478,14 @@
       <c r="G4">
         <v>6</v>
       </c>
-      <c r="H4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="H4">
+        <v>5</v>
+      </c>
+      <c r="I4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -3502,37 +3507,43 @@
       <c r="G5">
         <v>5</v>
       </c>
-      <c r="H5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>-7</v>
+      </c>
+      <c r="C6">
+        <v>-7</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
         <v>2</v>
       </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>-1</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>11</v>
-      </c>
       <c r="F6">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="H6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -3554,89 +3565,101 @@
       <c r="G7">
         <v>1</v>
       </c>
-      <c r="H7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B8">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E8">
+        <v>11</v>
+      </c>
+      <c r="F8">
+        <v>10</v>
+      </c>
+      <c r="G8">
         <v>2</v>
       </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="H8">
+        <v>-1</v>
+      </c>
+      <c r="I8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9">
+        <v>-1</v>
+      </c>
+      <c r="C9">
+        <v>-2</v>
+      </c>
+      <c r="D9">
+        <v>-11</v>
+      </c>
+      <c r="E9">
+        <v>-12</v>
+      </c>
+      <c r="F9">
+        <v>-13</v>
+      </c>
+      <c r="G9">
+        <v>-11</v>
+      </c>
+      <c r="H9">
+        <v>-5</v>
+      </c>
+      <c r="I9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B9">
+      <c r="B10">
         <v>-4</v>
       </c>
-      <c r="C9">
+      <c r="C10">
         <v>-6</v>
       </c>
-      <c r="D9">
+      <c r="D10">
         <v>-1</v>
       </c>
-      <c r="E9">
+      <c r="E10">
         <v>-4</v>
       </c>
-      <c r="F9">
+      <c r="F10">
         <v>4</v>
       </c>
-      <c r="G9">
+      <c r="G10">
         <v>-6</v>
       </c>
-      <c r="H9" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10">
-        <v>-1</v>
-      </c>
-      <c r="C10">
-        <v>-2</v>
-      </c>
-      <c r="D10">
-        <v>-11</v>
-      </c>
-      <c r="E10">
-        <v>-12</v>
-      </c>
-      <c r="F10">
-        <v>-13</v>
-      </c>
-      <c r="G10">
-        <v>-11</v>
-      </c>
-      <c r="H10" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="H10">
+        <v>-10</v>
+      </c>
+      <c r="I10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
@@ -3658,7 +3681,10 @@
       <c r="G11">
         <v>-16</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11">
+        <v>-17</v>
+      </c>
+      <c r="I11" t="s">
         <v>94</v>
       </c>
     </row>

--- a/data/leagues/Brown Munde 2026.xlsx
+++ b/data/leagues/Brown Munde 2026.xlsx
@@ -247,16 +247,16 @@
     <t>11.6-2.3-0.1</t>
   </si>
   <si>
+    <t>8.8-5.2-0.1</t>
+  </si>
+  <si>
     <t>8.7-5.3-0.1</t>
   </si>
   <si>
-    <t>8.3-5.6-0.1</t>
-  </si>
-  <si>
     <t>8.2-5.7-0.1</t>
   </si>
   <si>
-    <t>6.7-7.2-0.1</t>
+    <t>6.8-7.1-0.1</t>
   </si>
   <si>
     <t>6.0-7.9-0.1</t>
@@ -265,7 +265,7 @@
     <t>4.7-9.3-0.1</t>
   </si>
   <si>
-    <t>3.4-10.6-0.1</t>
+    <t>3.2-10.7</t>
   </si>
   <si>
     <t>3.4-10.5-0.1</t>
@@ -1779,19 +1779,19 @@
         <v>9</v>
       </c>
       <c r="B2">
-        <v>85.3</v>
+        <v>88</v>
       </c>
       <c r="C2">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="D2">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E2">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F2">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1817,28 +1817,28 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>7.7</v>
+        <v>5.7</v>
       </c>
       <c r="C3">
-        <v>34.3</v>
+        <v>36.4</v>
       </c>
       <c r="D3">
-        <v>22.4</v>
+        <v>25.4</v>
       </c>
       <c r="E3">
-        <v>17.2</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="G3">
-        <v>6.1</v>
+        <v>2.9</v>
       </c>
       <c r="H3">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="I3">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1847,7 +1847,7 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>98.09999999999999</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1855,28 +1855,28 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="C4">
-        <v>25.4</v>
+        <v>23.8</v>
       </c>
       <c r="D4">
-        <v>25.1</v>
+        <v>26.5</v>
       </c>
       <c r="E4">
-        <v>18.6</v>
+        <v>19.1</v>
       </c>
       <c r="F4">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="G4">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="H4">
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
       <c r="I4">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1885,7 +1885,7 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>94.3</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1893,37 +1893,37 @@
         <v>0</v>
       </c>
       <c r="B5">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="C5">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="D5">
-        <v>19.4</v>
+        <v>16.4</v>
       </c>
       <c r="E5">
-        <v>22.2</v>
+        <v>20.9</v>
       </c>
       <c r="F5">
-        <v>20.1</v>
+        <v>22.9</v>
       </c>
       <c r="G5">
-        <v>13.6</v>
+        <v>15</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I5">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J5">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>90</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1931,37 +1931,37 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>12.3</v>
+        <v>14.9</v>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>17.6</v>
       </c>
       <c r="E6">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="F6">
-        <v>19.5</v>
+        <v>19.1</v>
       </c>
       <c r="G6">
-        <v>15.7</v>
+        <v>15.4</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="I6">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J6">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>89.59999999999999</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1975,31 +1975,31 @@
         <v>2.6</v>
       </c>
       <c r="D7">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="E7">
-        <v>12.8</v>
+        <v>13.2</v>
       </c>
       <c r="F7">
-        <v>18.6</v>
+        <v>17.9</v>
       </c>
       <c r="G7">
-        <v>28.3</v>
+        <v>29.3</v>
       </c>
       <c r="H7">
-        <v>22.9</v>
+        <v>23.7</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="J7">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>68.59999999999999</v>
+        <v>69.8</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2013,28 +2013,28 @@
         <v>0.9</v>
       </c>
       <c r="D8">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="E8">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="F8">
-        <v>14.6</v>
+        <v>13.6</v>
       </c>
       <c r="G8">
-        <v>22.5</v>
+        <v>23.1</v>
       </c>
       <c r="H8">
-        <v>32.4</v>
+        <v>31.5</v>
       </c>
       <c r="I8">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="J8">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="K8">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="L8">
         <v>48.7</v>
@@ -2051,31 +2051,31 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E9">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="F9">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="G9">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="H9">
-        <v>14.1</v>
+        <v>15</v>
       </c>
       <c r="I9">
-        <v>40.4</v>
+        <v>42</v>
       </c>
       <c r="J9">
-        <v>26</v>
+        <v>24.8</v>
       </c>
       <c r="K9">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="L9">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -2095,25 +2095,25 @@
         <v>0.1</v>
       </c>
       <c r="F10">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H10">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="I10">
-        <v>18.1</v>
+        <v>13</v>
       </c>
       <c r="J10">
-        <v>29.9</v>
+        <v>30.1</v>
       </c>
       <c r="K10">
-        <v>48.2</v>
+        <v>53.1</v>
       </c>
       <c r="L10">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2133,25 +2133,25 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G11">
         <v>0.6</v>
       </c>
       <c r="H11">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I11">
-        <v>17.8</v>
+        <v>20.2</v>
       </c>
       <c r="J11">
-        <v>37.6</v>
+        <v>39.6</v>
       </c>
       <c r="K11">
-        <v>39.9</v>
+        <v>35.7</v>
       </c>
       <c r="L11">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>
@@ -2195,22 +2195,22 @@
         <v>9</v>
       </c>
       <c r="B2">
-        <v>72.09999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="C2">
-        <v>94.19999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="D2">
-        <v>95.5</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="E2">
-        <v>99.5</v>
+        <v>99.3</v>
       </c>
       <c r="F2">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="G2">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="H2">
         <v>100</v>
@@ -2233,19 +2233,19 @@
         <v>97.59999999999999</v>
       </c>
       <c r="E3">
-        <v>96.3</v>
+        <v>97.7</v>
       </c>
       <c r="F3">
-        <v>70.7</v>
+        <v>68.7</v>
       </c>
       <c r="G3">
-        <v>93.7</v>
+        <v>93.8</v>
       </c>
       <c r="H3">
-        <v>98.3</v>
+        <v>98.5</v>
       </c>
       <c r="I3">
-        <v>98.3</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2253,86 +2253,86 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>8.300000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="C4">
-        <v>44.2</v>
+        <v>43.9</v>
       </c>
       <c r="D4">
-        <v>52.8</v>
+        <v>55.3</v>
       </c>
       <c r="E4">
-        <v>95.59999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="F4">
-        <v>81.8</v>
+        <v>80.2</v>
       </c>
       <c r="G4">
-        <v>94.8</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="H4">
-        <v>95.3</v>
+        <v>96.5</v>
       </c>
       <c r="I4">
-        <v>95.8</v>
+        <v>94.89999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B5">
-        <v>99.90000000000001</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="C5">
-        <v>49.5</v>
+        <v>18.3</v>
       </c>
       <c r="D5">
-        <v>95.39999999999999</v>
+        <v>18.8</v>
       </c>
       <c r="E5">
-        <v>97.2</v>
+        <v>18.8</v>
       </c>
       <c r="F5">
-        <v>95.89999999999999</v>
+        <v>36.2</v>
       </c>
       <c r="G5">
-        <v>95.39999999999999</v>
+        <v>72.89999999999999</v>
       </c>
       <c r="H5">
-        <v>86.90000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="I5">
-        <v>90.40000000000001</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B6">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C6">
-        <v>17.2</v>
+        <v>51.2</v>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>93.5</v>
       </c>
       <c r="E6">
-        <v>18.1</v>
+        <v>96.89999999999999</v>
       </c>
       <c r="F6">
-        <v>36</v>
+        <v>96.2</v>
       </c>
       <c r="G6">
-        <v>73</v>
+        <v>96.39999999999999</v>
       </c>
       <c r="H6">
-        <v>90.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I6">
-        <v>89.90000000000001</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2340,28 +2340,28 @@
         <v>3</v>
       </c>
       <c r="B7">
-        <v>78.60000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="C7">
-        <v>88</v>
+        <v>86.5</v>
       </c>
       <c r="D7">
-        <v>62.4</v>
+        <v>62.1</v>
       </c>
       <c r="E7">
-        <v>91.10000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="F7">
-        <v>75.59999999999999</v>
+        <v>78.10000000000001</v>
       </c>
       <c r="G7">
-        <v>45.8</v>
+        <v>48.7</v>
       </c>
       <c r="H7">
-        <v>72.8</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="I7">
-        <v>67.7</v>
+        <v>69.19999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2372,25 +2372,25 @@
         <v>100</v>
       </c>
       <c r="C8">
-        <v>98.09999999999999</v>
+        <v>98</v>
       </c>
       <c r="D8">
-        <v>69.39999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="E8">
-        <v>61.4</v>
+        <v>59.2</v>
       </c>
       <c r="F8">
-        <v>90.7</v>
+        <v>92.5</v>
       </c>
       <c r="G8">
-        <v>77.40000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="H8">
-        <v>45.3</v>
+        <v>45.1</v>
       </c>
       <c r="I8">
-        <v>48.7</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2401,80 +2401,80 @@
         <v>0.2</v>
       </c>
       <c r="C9">
-        <v>9.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="D9">
-        <v>14.9</v>
+        <v>16.5</v>
       </c>
       <c r="E9">
-        <v>7.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F9">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="G9">
-        <v>11.1</v>
+        <v>10.2</v>
       </c>
       <c r="H9">
+        <v>7.6</v>
+      </c>
+      <c r="I9">
         <v>9</v>
-      </c>
-      <c r="I9">
-        <v>8.1</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B10">
-        <v>11.7</v>
+        <v>37.3</v>
       </c>
       <c r="C10">
-        <v>3.2</v>
+        <v>93.7</v>
       </c>
       <c r="D10">
-        <v>13.7</v>
+        <v>78.3</v>
       </c>
       <c r="E10">
-        <v>4.9</v>
+        <v>30.8</v>
       </c>
       <c r="F10">
-        <v>17.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G10">
-        <v>4.399999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="H10">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="I10">
-        <v>0.6</v>
+        <v>0.8999999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B11">
-        <v>37.2</v>
+        <v>11.7</v>
       </c>
       <c r="C11">
-        <v>96.59999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="D11">
-        <v>78.3</v>
+        <v>13.9</v>
       </c>
       <c r="E11">
-        <v>28.8</v>
+        <v>3.3</v>
       </c>
       <c r="F11">
-        <v>8.200000000000001</v>
+        <v>14.7</v>
       </c>
       <c r="G11">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="H11">
-        <v>0.8999999999999999</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="I11">
         <v>0.5</v>
@@ -2891,7 +2891,7 @@
         <v>918.52</v>
       </c>
       <c r="F3">
-        <v>98.09999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -2920,13 +2920,13 @@
         <v>836.3</v>
       </c>
       <c r="F4">
-        <v>94.3</v>
+        <v>95.5</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I4" t="s">
         <v>83</v>
@@ -2949,13 +2949,13 @@
         <v>791.36</v>
       </c>
       <c r="F5">
-        <v>90</v>
+        <v>89.3</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I5" t="s">
         <v>84</v>
@@ -2978,7 +2978,7 @@
         <v>784.1199999999999</v>
       </c>
       <c r="F6">
-        <v>89.60000000000001</v>
+        <v>89</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -3007,7 +3007,7 @@
         <v>839.0799999999999</v>
       </c>
       <c r="F7">
-        <v>68.60000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -3039,7 +3039,7 @@
         <v>48.7</v>
       </c>
       <c r="G8">
-        <v>0.8999999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="H8" t="s">
         <v>78</v>
@@ -3065,10 +3065,10 @@
         <v>726.9400000000001</v>
       </c>
       <c r="F9">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="G9">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="H9" t="s">
         <v>79</v>
@@ -3094,10 +3094,10 @@
         <v>693.4400000000001</v>
       </c>
       <c r="F10">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="G10">
-        <v>48.2</v>
+        <v>53.1</v>
       </c>
       <c r="H10" t="s">
         <v>80</v>
@@ -3123,10 +3123,10 @@
         <v>710.36</v>
       </c>
       <c r="F11">
-        <v>0.7000000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="G11">
-        <v>39.90000000000001</v>
+        <v>35.7</v>
       </c>
       <c r="H11" t="s">
         <v>81</v>
@@ -3227,19 +3227,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D5">
         <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3247,19 +3247,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D6">
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3487,60 +3487,60 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="C5">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>4</v>
       </c>
       <c r="I5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>-5</v>
+      </c>
+      <c r="C6">
+        <v>-4</v>
+      </c>
+      <c r="D6">
+        <v>-1</v>
+      </c>
+      <c r="E6">
+        <v>-1</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
         <v>5</v>
-      </c>
-      <c r="B6">
-        <v>-7</v>
-      </c>
-      <c r="C6">
-        <v>-7</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
       </c>
       <c r="H6">
         <v>4</v>
       </c>
       <c r="I6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:9">
